--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -426,26 +426,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D141"/>
+  <dimension ref="A1:E141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>频道名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>MP4名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>是否发布</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>是否已经发布</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -454,1962 +459,2666 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>99%的人都誤解了!金剛乘的雙修到底是什麽？雙運法背後的覺悟之路#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-06-02 06:02:03</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>《六祖壇經》裏泄露天機的五句話：修行有成，「三身」便是成果。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>《心經》結尾咒語：“揭諦揭諦”是什麼意思？99%的人都理解錯了！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
       <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>《心經》隱藏的秘密，何為”諸法空相“，它不是虛無而是無限可能。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>《成唯識論》揭示，末法時代聖者現世五大征兆，輪回五層次的奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
       <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>不去掃墓就是不孝嗎？廣欽老和尚的開示，讓人明白了真正的孝道。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
       <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>不知乞討的人真假，到底要不要布施，高僧一句話點醒迷茫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
       <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>二十分鐘講透佛教的三界與六道，釋迦牟尼不為人知的宇宙！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
       <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>佛學中的「禪」有何意義？修行者「覺悟」的終極智慧。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
       <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>佛教七大密咒，竟隱藏能量共振原理，持念消災增福奧祕解析。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
       <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>佛教千年難解的謎題，業報到底是誰的？前世所做你該承擔嗎？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
       <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>佛教所說的極樂世界到底在哪裏？念佛真的能脫離輪回嗎？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
       <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>佛教的三千大千世界究竟有多大？他與科學的宇宙觀有什麽共通點？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
       <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>佛教的四大菩薩都是誰？他們如何成就眾生的覺悟之路。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
       <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>佛教的最高真理，中道智慧，超越對立終極覺悟的奧祕！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
       <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>佛法三境界，空為無執、色為顯相、幻為虛妄，參透關鍵即得大解脫。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
       <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>佛法的悖論，為何“無我”還要“輪迴”，到底是誰在承受因果？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
       <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>佛道雙修！超越凡俗的修行秘訣，從煉氣入門到陽神出遊的完整指引！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>佛陀2500年前已發現，宇宙最神祕力量，因果相續如何影響命運。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
       <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>佛陀2500年前的預言，五濁惡世已降臨，解脫之道就在這裏。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
       <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>佛陀三身之謎，法身、報身、應身，哪一身才是真正的佛？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
       <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>佛陀在燈下為弟子講解，影子消失的道理，原來這才是真正的解脫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
       <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>佛陀慈悲開示，這七種無財布施法，不用花錢也能獲大福報。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
       <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>佛陀慈悲開示：五蘊皆空之後還有一物，悟此可直接超越三界。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
       <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>佛陀慈悲開示：每個人身上的疾病，其實是前世所欠之債的清算。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
       <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>佛陀涅槃前點化迦葉，真修行者不拘泥形式，而是通達這四種內心境界。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
       <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>佛陀用一片落葉，向阿難開示驚人秘密，我不是第一位佛。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
       <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>佛陀的五時說法到底是什麽？從華嚴到涅槃，成佛的秘密就在這裏！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
       <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>佛陀的女弟子蓮華色，曾犯下亂倫罪過的她，是如何修成神通第一的。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
       <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>佛陀的矛盾指引，放下慾望卻要成佛，揭秘背後的驚人智慧！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
       <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>佛陀祕傳居家八法，在家修行人虔心領悟，今生來世皆安樂。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
       <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>佛陀說眾生皆可成佛，為何我們還在輪回？原來缺失最重要的三步。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
       <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>佛陀開示弟子：夫妻緣分從何而來，今生相遇有何因果聯繫？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
       <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>佛陀開示阿難：心不在身內，也不在身外！阿難聽後頓時茅塞頓開。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
       <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>佛陀開示：命中有時終須有，人生這3件事早有安排，順勢而為！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
       <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>佛陀點化阿難，真假佛法怎麽分辨，真正佛法的四大標誌。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
       <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>佛陀點破夫妻因果：為何夫妻緣盡便成冤？三世因果早已註定。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
       <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>你對誰生嗔恨，就會與誰轉世為親，因果業力循環藏何秘密？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
       <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>修行者到底能不能吃雞蛋？印光大師的開示，道出佛教戒律真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
       <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>修行路上的三大障礙：眼淫、心淫、意淫，龍樹菩薩親傳破解奧秘！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
       <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>全球人口負增長，六道輪迴也會重組嗎？文殊菩薩揭示五大奧祕！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
       <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>六祖慧能金身千年不腐，卻遭遇3次劫難，最後1次幾乎被毀！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
       <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>六祖慧能點化：做這件事可消三生罪業，福報不請自來。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
       <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>刀師村長質問佛陀，佛法普渡眾生了嗎？佛陀用兩個比喻揭示傳法真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
       <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>十四分鐘徹底讀懂《心經》，260字竟隱藏著成佛奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
       <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>唵嘛呢叭咪吽有何奧妙？藥師佛揭示：六字真言蘊含的不凡能量。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
       <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>因果報應有多可怕，佛陀親口警示，修行者絕對不能觸碰的3大禁忌。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
       <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>地藏王菩薩告誡：人去世後到陰間必經這九關，看完生前必修功德。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
       <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>地藏王菩薩揭示，清明節不要隨便燒紙錢，這三樣才是亡者真正需要。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
       <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>地藏王菩薩開示：頭七超度的重要意義，這七天對亡者至關重要。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
       <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>地藏王菩薩：少跟孩子置氣，他們選擇你為父母，有這三種原因！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
       <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>外道沙門師傅詆毀佛法，眾比丘憤而議論，佛陀的教誨令所有人頓悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
       <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>大勢至菩薩開示：人在投胎前，為何會自己選擇父母，背後原因令人深思。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
       <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>大勢至菩薩開示：末法時代紛擾世界，保持內心平靜的終極奧秘！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
       <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>大勢至菩薩點化：當六根不凈時，這個修行秘訣讓你立刻心如止水。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
       <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>大梵天王問佛陀：何為空中妙有？佛陀回答揭示覺知奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
       <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>大迦葉問佛陀，為何修行人要斷除色欲？元神外泄導致修行受阻。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
       <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>大迦葉問佛陀：為何亡者於人間徘徊七日，佛陀揭示陰陽兩界奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
       <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>大迦葉問釋迦牟尼：成佛前為何要履行生子義務？真相讓所有人覺悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
       <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>女子跪問佛陀，為何不能散父親骨灰？佛陀揭示輪回奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
       <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>學佛之人切記，千萬別做這三件事，會耗光你的福報。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
       <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>學佛人不可不知，佛前十種供品的寓意和果報，正確供養才能修行圓滿。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
       <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>家裡有“髒東西”怎麼辦？持念這一佛教咒語，驅邪避凶最為靈驗！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
       <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>富樓那問釋迦牟尼：您說無生無滅，那麽哪來的六道輪回呢？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
       <c r="C65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>帝釋天三問釋迦牟尼：「何為善」？佛陀的回答揭示人生大智慧。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
       <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>帝釋天三問釋迦牟尼：輪回的盡頭是什麽？佛陀的開示令所有人頓悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
       <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>帝釋天問佛陀：何為菩提心？佛陀只用三個字，讓在場修行者瞬間開悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
       <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>廣欽老和尚開示，如何做到一心不亂，領悟這三點當下即解脫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
       <c r="C69" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>彌勒佛問佛陀，何為究竟解脫，一句話讓眾人頓悟涅槃。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
       <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>彌勒菩薩指引，轉世的真諦是什麼？超越生死才是究竟解脫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
       <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>心經中“究竟涅槃”的境界是什麼？大勢至菩薩的開示，讓眾人悟道修行真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
       <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>念佛不見佛現身，我們到底在求誰，禪師點破道理妙不可言！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
       <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>探索密教深奧智慧！揭示寧瑪派傳世秘法與大圓滿修行的真實內涵！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>1</v>
-      </c>
       <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>文殊菩薩問釋迦牟尼：何為無上正覺？佛陀的回答讓众人醍醐灌頂。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
       <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>文殊菩薩開示：不要迷戀容貌出眾者，修行後才知外表的前世因緣！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>1</v>
-      </c>
       <c r="C76" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>文殊菩薩開示：在家居士最容易犯的三個錯誤，小心毀掉你的福報。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>1</v>
-      </c>
       <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>文殊菩薩開示：錢財具有靈性，銘記4句真言能財富相隨！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
       <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>文殊菩薩點化：君子之交淡如水，佛門中的交友之道令人深思！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>1</v>
-      </c>
       <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>普賢菩薩十大行願，為何會獨缺一行，這個空白隱含什麽修行奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>1</v>
-      </c>
       <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>普賢菩薩開示，一即一切，一切即一，其中蘊含佛法發人深省。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
       <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>智光禪師臨終前點撥，福報只有一條路可獲得，那就是放棄福報！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
       <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>最强菩萨，地獄之主普渡眾生，20分鐘徹底了解地藏王菩薩。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>1</v>
-      </c>
       <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>最疼愛你的母親，竟是前世被你傷害過的人，佛陀開示因果輪回奧妙。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
       <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>末法時代修行人必看，踏入這五種學佛誤區，只會讓佛菩薩越來越遠。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
       <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>末法時代如何修行？釋迦牟尼開示阿難，這三種人最易圓滿！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
       <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>末法時期如何修行？佛陀與藥師如來對話，揭示化解病苦的三大法門。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
       <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>比丘問佛陀：色即是空，既然諸色皆空，為何修行之人要遠離女色。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
       <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>比丘問釋迦牟尼，何為眾生平等四相皆空，佛陀開示人同狗並無分別。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
       <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>比丘尼問釋迦牟尼：女人為何難成佛？佛陀開示讓眾人豁然開朗。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
       <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>波斯匿王問佛陀：為何布施越多福報越少，一個故事點破布施因果奧妙。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
       <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>波斯匿迦問佛陀，「我」究竟是什麽？，佛陀開示無我觀的奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
       <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>涅槃寂靜，佛陀親授的終極解脫奧祕，一念之間超越生死。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
       <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>為什麼好人沒好報？高僧秘密開示：福報被“偷走”的3個徵兆！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
       <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>為什麽佛說法四十九年，未曾說過一字？卻點亮無量眾生智慧，真相讓人驚嘆！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>1</v>
-      </c>
       <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>為什麽佛陀說：持咒不如修心？一個漁夫的故事道破了修行的奥秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
       <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>為什麽說「十小咒」擁有無量功德？短短幾句就能往生極樂，祛病消災福慧雙增#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
       <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>為何佛陀涅槃後，大迦葉與阿難爆發激烈爭執？竟藏著佛教分裂真相。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
       <c r="C98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>為何大德都說，2025年正月要誦讀金剛經？竟然蘊含著轉運玄機。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>1</v>
-      </c>
       <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>為何高僧大德皆言，春節要讀地藏經？原來暗含這個修行機緣。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>1</v>
-      </c>
       <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>現今所說的四大皆空理念竟是錯誤的，這才是佛教「緣起論」的真正邏輯！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
       <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>目犍連問佛陀：親人真的會在六道重逢嗎？佛陀的開示讓眾人淚目！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
       <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>目犍連示現五神通，佛陀告誡弟子，修行為解脫而非神通。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>1</v>
-      </c>
       <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>禪宗千年難題，執著與放下之間，如何找到菩提之路？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>1</v>
-      </c>
       <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>維摩詰假病示疾，揭露「在家成佛」的五個陷阱！你踩中幾條？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
       <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>維摩詰問佛陀：在家與出家修行有何不同？佛陀一語道破精進要訣。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>1</v>
-      </c>
       <c r="C106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>維摩詰問佛陀：生死之間究竟相隔多遠？佛陀用一片落葉揭示輪回。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B107" t="n">
-        <v>1</v>
-      </c>
       <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>維摩詰開示弟子：做善事也會損耗福德，這四個標準才是行善關鍵。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B108" t="n">
-        <v>1</v>
-      </c>
       <c r="C108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>耆婆問釋迦牟尼：為何病人會痛苦？佛陀回答道出了生命真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>1</v>
-      </c>
       <c r="C109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>舍利弗問釋迦牟尼：世尊您教導無住無執，為何又要世人皈依三寶。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
       <c r="C110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>虛空藏菩薩財富法，傳授五大富貴秘訣，第四訣改變命運軌跡。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>1</v>
-      </c>
       <c r="C111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>西方極樂世界真的存在嗎？該如如何到達？原來也沒那麽難。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B112" t="n">
-        <v>1</v>
-      </c>
       <c r="C112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>觀世音菩薩問佛陀：人死後真的會投胎嗎？佛陀的開示讓人徹悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>1</v>
-      </c>
       <c r="C113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>觀世音菩薩開示：老天要渡化你，會給你五種提醒，要留意！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>1</v>
-      </c>
       <c r="C114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>觀音菩薩開示：供奉佛像時四個禁忌，很多人不知道一直在犯。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>1</v>
-      </c>
       <c r="C115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>觀音菩薩開示：真正有慈悲之人，不是天天拜佛，而是具有這三種品性。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>1</v>
-      </c>
       <c r="C116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>解讀《心經》，何爲“般若波羅蜜”，領悟佛法的終極智慧。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>1</v>
-      </c>
       <c r="C117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>言多語失造口業，觀音菩薩開示：修習這三種口德可避災禍！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
       <c r="C118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>超度亡者時，是念「地藏經」，還是念「往生咒」，高僧開示區別很大。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>1</v>
-      </c>
       <c r="C119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>迦旃延問釋迦牟尼：世尊您教導無相，為何又要世人供養佛像。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>1</v>
-      </c>
       <c r="C120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>達摩祖師點化弟子：參禪難在求玄妙，悟得此道方為妙法。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>1</v>
-      </c>
       <c r="C121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>釋迦牟尼佛為何斷言人生皆苦？十分鐘講透佛教四聖諦真相#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
       <c r="C122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>釋迦牟尼：真正開悟的人都會具有這三種狀態。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
       <c r="C123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>阿難問佛陀：面對災禍，佛菩薩為何不普渡眾生，原來這兩種情況無法救度。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>1</v>
-      </c>
       <c r="C124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼佛：涅槃是新生還是他生？佛陀回答讓眾生頓悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>1</v>
-      </c>
       <c r="C125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼，如何區分真假開悟，佛陀用四句話讓眾人徹悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>1</v>
-      </c>
       <c r="C126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：世尊為何不開創凈土？佛陀的回答讓人頓悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>1</v>
-      </c>
       <c r="C127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：人為何會有生死？佛陀回答道出生死真相。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>1</v>
-      </c>
       <c r="C128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：您涅槃之後還會輪回嗎？佛陀的回答令眾生頓悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>1</v>
-      </c>
       <c r="C129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
+      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：為何修行越深心魔越強？佛陀指出了關鍵盲點！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>1</v>
-      </c>
       <c r="C130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
+      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>阿難問：世尊教導不執著，為何對佛法如此珍重？佛陀回答令人深思。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>1</v>
-      </c>
       <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>阿難尊者親歷，觀世音菩薩顯靈傳授，讓祈求必成的三個發願法則！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>1</v>
-      </c>
       <c r="C132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
+      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>阿難開示比丘，心淫比身淫更傷修行，領悟此法可助斷欲修身。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>1</v>
-      </c>
       <c r="C133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>隨喜加入，同修善法，南無阿彌陀佛！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>1</v>
-      </c>
       <c r="C134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>須菩提問佛陀，什麽是「無生法忍」，文殊菩薩道破修行終極奧義。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>1</v>
-      </c>
       <c r="C135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
+      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>須菩提問佛陀：世間苦難何時了？佛陀妙語開示眾人醒悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B136" t="n">
-        <v>1</v>
-      </c>
       <c r="C136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>須達多問佛陀：為何好人早逝，惡人長壽，一個故事揭開三世因果真相。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>1</v>
-      </c>
       <c r="C137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>須達多問釋迦牟尼：佛陀您教導布施，為何還要弟子日日托缽。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>1</v>
-      </c>
       <c r="C138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
+      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>颠覆你对佛法的认知！99%的人都误解的修行真相，佛教真正的秘密首次揭露！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
       <c r="C139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
+      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>體內住著兩個“自己”？佛陀：識得“元神”，方能跳出輪迴！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>1</v>
-      </c>
       <c r="C140" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>鬼怕哪種人？佛說：有3種人，連鬼也不敢靠近他！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>1</v>
-      </c>
       <c r="C141" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
+      <c r="E141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2422,26 +3131,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D143"/>
+  <dimension ref="A1:E143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>频道名称</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
           <t>MP4名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>是否发布</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>是否已经发布</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -2450,1990 +3164,2558 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>99%的人都誤解了!金剛乘的雙修到底是什麽？雙運法背後的覺悟之路#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="n">
-        <v>0</v>
-      </c>
-      <c r="D2" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>《六祖壇經》裏泄露天機的五句話：修行有成，「三身」便是成果。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
       <c r="C3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>《心經》結尾咒語：“揭諦揭諦”是什麼意思？99%的人都理解錯了！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
       <c r="C4" t="n">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>《心經》隱藏的秘密，何為”諸法空相“，它不是虛無而是無限可能。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>1</v>
-      </c>
       <c r="C5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>《成唯識論》揭示，末法時代聖者現世五大征兆，輪回五層次的奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>1</v>
-      </c>
       <c r="C6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
           <t>不去掃墓就是不孝嗎？廣欽老和尚的開示，讓人明白了真正的孝道。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>1</v>
-      </c>
       <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
           <t>不知乞討的人真假，到底要不要布施，高僧一句話點醒迷茫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B8" t="n">
-        <v>1</v>
-      </c>
       <c r="C8" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>二十分鐘講透佛教的三界與六道，釋迦牟尼不為人知的宇宙！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1</v>
-      </c>
       <c r="C9" t="n">
-        <v>0</v>
-      </c>
-      <c r="D9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>佛學中的「禪」有何意義？修行者「覺悟」的終極智慧。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>1</v>
-      </c>
       <c r="C10" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
           <t>佛教七大密咒，竟隱藏能量共振原理，持念消災增福奧祕解析。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
       <c r="C11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
           <t>佛教千年難解的謎題，業報到底是誰的？前世所做你該承擔嗎？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B12" t="n">
-        <v>1</v>
-      </c>
       <c r="C12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
           <t>佛教所說的極樂世界到底在哪裏？念佛真的能脫離輪回嗎？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
       <c r="C13" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
           <t>佛教的三千大千世界究竟有多大？他與科學的宇宙觀有什麽共通點？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B14" t="n">
-        <v>1</v>
-      </c>
       <c r="C14" t="n">
-        <v>0</v>
-      </c>
-      <c r="D14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
           <t>佛教的四大菩薩都是誰？他們如何成就眾生的覺悟之路。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B15" t="n">
-        <v>1</v>
-      </c>
       <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
           <t>佛教的最高真理，中道智慧，超越對立終極覺悟的奧祕！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B16" t="n">
-        <v>1</v>
-      </c>
       <c r="C16" t="n">
-        <v>0</v>
-      </c>
-      <c r="D16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>佛法三境界，空為無執、色為顯相、幻為虛妄，參透關鍵即得大解脫。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
       <c r="C17" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
           <t>佛法的悖論，為何“無我”還要“輪迴”，到底是誰在承受因果？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
       <c r="C18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
           <t>佛道雙修！超越凡俗的修行秘訣，從煉氣入門到陽神出遊的完整指引！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
       <c r="C19" t="n">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
           <t>佛陀2500年前已發現，宇宙最神祕力量，因果相續如何影響命運。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
       <c r="C20" t="n">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
           <t>佛陀2500年前的預言，五濁惡世已降臨，解脫之道就在這裏。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
       <c r="C21" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
           <t>佛陀三身之謎，法身、報身、應身，哪一身才是真正的佛？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
       <c r="C22" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
           <t>佛陀在燈下為弟子講解，影子消失的道理，原來這才是真正的解脫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B23" t="n">
-        <v>1</v>
-      </c>
       <c r="C23" t="n">
-        <v>0</v>
-      </c>
-      <c r="D23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
           <t>佛陀慈悲開示，這七種無財布施法，不用花錢也能獲大福報。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
       <c r="C24" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>佛陀慈悲開示：五蘊皆空之後還有一物，悟此可直接超越三界。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B25" t="n">
-        <v>1</v>
-      </c>
       <c r="C25" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
           <t>佛陀慈悲開示：每個人身上的疾病，其實是前世所欠之債的清算。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>1</v>
-      </c>
       <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
           <t>佛陀涅槃前點化迦葉，真修行者不拘泥形式，而是通達這四種內心境界。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
       <c r="C27" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
           <t>佛陀用一片落葉，向阿難開示驚人秘密，我不是第一位佛。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
       <c r="C28" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>佛陀的五時說法到底是什麽？從華嚴到涅槃，成佛的秘密就在這裏！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
       <c r="C29" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
           <t>佛陀的女弟子蓮華色，曾犯下亂倫罪過的她，是如何修成神通第一的。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
       <c r="C30" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
           <t>佛陀的矛盾指引，放下慾望卻要成佛，揭秘背後的驚人智慧！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B31" t="n">
-        <v>1</v>
-      </c>
       <c r="C31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
           <t>佛陀祕傳居家八法，在家修行人虔心領悟，今生來世皆安樂。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
       <c r="C32" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
           <t>佛陀說眾生皆可成佛，為何我們還在輪回？原來缺失最重要的三步。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
       <c r="C33" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
           <t>佛陀開示弟子：夫妻緣分從何而來，今生相遇有何因果聯繫？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
       <c r="C34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
           <t>佛陀開示眾弟子：命中注定與自由意志，到底該如何平衡！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B35" t="n">
-        <v>1</v>
-      </c>
       <c r="C35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D35" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
           <t>佛陀開示阿難：心不在身內，也不在身外！阿難聽後頓時茅塞頓開。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
       <c r="C36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D36" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
           <t>佛陀開示：命中有時終須有，人生這3件事早有安排，順勢而為！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
       <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
           <t>佛陀點化阿難，真假佛法怎麽分辨，真正佛法的四大標誌。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
       <c r="C38" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D38" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
           <t>佛陀點破夫妻因果：為何夫妻緣盡便成冤？三世因果早已註定。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
       <c r="C39" t="n">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
           <t>你對誰生嗔恨，就會與誰轉世為親，因果業力循環藏何秘密？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
       <c r="C40" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D40" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
           <t>修行者到底能不能吃雞蛋？印光大師的開示，道出佛教戒律真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
       <c r="C41" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D41" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
           <t>修行路上的三大障礙：眼淫、心淫、意淫，龍樹菩薩親傳破解奧秘！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
       <c r="C42" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D42" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
           <t>全球人口負增長，六道輪迴也會重組嗎？文殊菩薩揭示五大奧祕！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
       <c r="C43" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D43" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
           <t>六祖慧能金身千年不腐，卻遭遇3次劫難，最後1次幾乎被毀！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
       <c r="C44" t="n">
-        <v>0</v>
-      </c>
-      <c r="D44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D44" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
           <t>六祖慧能點化：做這件事可消三生罪業，福報不請自來。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B45" t="n">
-        <v>1</v>
-      </c>
       <c r="C45" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D45" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
           <t>刀師村長質問佛陀，佛法普渡眾生了嗎？佛陀用兩個比喻揭示傳法真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
       <c r="C46" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D46" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
           <t>十四分鐘徹底讀懂《心經》，260字竟隱藏著成佛奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
       <c r="C47" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D47" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
           <t>唵嘛呢叭咪吽有何奧妙？藥師佛揭示：六字真言蘊含的不凡能量。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
       <c r="C48" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D48" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>因果報應有多可怕，佛陀親口警示，修行者絕對不能觸碰的3大禁忌。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
       <c r="C49" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D49" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
           <t>地藏王菩薩告誡：人去世後到陰間必經這九關，看完生前必修功德。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
       <c r="C50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D50" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
           <t>地藏王菩薩揭示，清明節不要隨便燒紙錢，這三樣才是亡者真正需要。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B51" t="n">
-        <v>1</v>
-      </c>
       <c r="C51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D51" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
           <t>地藏王菩薩開示：頭七超度的重要意義，這七天對亡者至關重要。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B52" t="n">
-        <v>1</v>
-      </c>
       <c r="C52" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D52" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
           <t>地藏王菩薩：少跟孩子置氣，他們選擇你為父母，有這三種原因！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
       <c r="C53" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D53" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
           <t>外道沙門師傅詆毀佛法，眾比丘憤而議論，佛陀的教誨令所有人頓悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
       <c r="C54" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D54" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
           <t>大勢至菩薩開示：人在投胎前，為何會自己選擇父母，背後原因令人深思。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
       <c r="C55" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D55" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
           <t>大勢至菩薩開示：末法時代紛擾世界，保持內心平靜的終極奧秘！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
       <c r="C56" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D56" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
           <t>大勢至菩薩點化：當六根不凈時，這個修行秘訣讓你立刻心如止水。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
       <c r="C57" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D57" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>大梵天王問佛陀：何為空中妙有？佛陀回答揭示覺知奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
       <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
           <t>大迦葉問佛陀，為何修行人要斷除色欲？元神外泄導致修行受阻。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B59" t="n">
-        <v>1</v>
-      </c>
       <c r="C59" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
           <t>大迦葉問佛陀：為何亡者於人間徘徊七日，佛陀揭示陰陽兩界奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
       <c r="C60" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D60" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
           <t>大迦葉問釋迦牟尼：成佛前為何要履行生子義務？真相讓所有人覺悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
       <c r="C61" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D61" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>女子跪問佛陀，為何不能散父親骨灰？佛陀揭示輪回奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
       <c r="C62" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D62" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
           <t>學佛之人切記，千萬別做這三件事，會耗光你的福報。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
       <c r="C63" t="n">
-        <v>0</v>
-      </c>
-      <c r="D63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D63" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
           <t>學佛人不可不知，佛前十種供品的寓意和果報，正確供養才能修行圓滿。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
       <c r="C64" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D64" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
           <t>家裡有“髒東西”怎麼辦？持念這一佛教咒語，驅邪避凶最為靈驗！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
       <c r="C65" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D65" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
           <t>富樓那問釋迦牟尼：您說無生無滅，那麽哪來的六道輪回呢？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
       <c r="C66" t="n">
-        <v>0</v>
-      </c>
-      <c r="D66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D66" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
           <t>帝釋天三問釋迦牟尼：「何為善」？佛陀的回答揭示人生大智慧。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
       <c r="C67" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D67" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
           <t>帝釋天三問釋迦牟尼：輪回的盡頭是什麽？佛陀的開示令所有人頓悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
       <c r="C68" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D68" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
           <t>帝釋天問佛陀：何為菩提心？佛陀只用三個字，讓在場修行者瞬間開悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
       <c r="C69" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D69" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
           <t>廣欽老和尚開示，如何做到一心不亂，領悟這三點當下即解脫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
       <c r="C70" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D70" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
           <t>彌勒佛問佛陀，何為究竟解脫，一句話讓眾人頓悟涅槃。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
       <c r="C71" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D71" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
           <t>彌勒菩薩指引，轉世的真諦是什麼？超越生死才是究竟解脫！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
       <c r="C72" t="n">
-        <v>0</v>
-      </c>
-      <c r="D72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D72" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
           <t>心經中“究竟涅槃”的境界是什麼？大勢至菩薩的開示，讓眾人悟道修行真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
       <c r="C73" t="n">
-        <v>0</v>
-      </c>
-      <c r="D73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D73" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
           <t>念佛不見佛現身，我們到底在求誰，禪師點破道理妙不可言！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>1</v>
-      </c>
       <c r="C74" t="n">
-        <v>0</v>
-      </c>
-      <c r="D74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
           <t>探索密教深奧智慧！揭示寧瑪派傳世秘法與大圓滿修行的真實內涵！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
       <c r="C75" t="n">
-        <v>0</v>
-      </c>
-      <c r="D75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
           <t>文殊菩薩問釋迦牟尼：何為無上正覺？佛陀的回答讓众人醍醐灌頂。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>1</v>
-      </c>
       <c r="C76" t="n">
-        <v>0</v>
-      </c>
-      <c r="D76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
           <t>文殊菩薩開示：不要迷戀容貌出眾者，修行後才知外表的前世因緣！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>1</v>
-      </c>
       <c r="C77" t="n">
-        <v>0</v>
-      </c>
-      <c r="D77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
           <t>文殊菩薩開示：在家居士最容易犯的三個錯誤，小心毀掉你的福報。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
       <c r="C78" t="n">
-        <v>0</v>
-      </c>
-      <c r="D78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
           <t>文殊菩薩開示：錢財具有靈性，銘記4句真言能財富相隨！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>1</v>
-      </c>
       <c r="C79" t="n">
-        <v>0</v>
-      </c>
-      <c r="D79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
           <t>文殊菩薩點化：君子之交淡如水，佛門中的交友之道令人深思！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>1</v>
-      </c>
       <c r="C80" t="n">
-        <v>0</v>
-      </c>
-      <c r="D80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
           <t>普賢菩薩十大行願，為何會獨缺一行，這個空白隱含什麽修行奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
       <c r="C81" t="n">
-        <v>0</v>
-      </c>
-      <c r="D81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
           <t>普賢菩薩開示，一即一切，一切即一，其中蘊含佛法發人深省。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
       <c r="C82" t="n">
-        <v>0</v>
-      </c>
-      <c r="D82" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
           <t>智光禪師臨終前點撥，福報只有一條路可獲得，那就是放棄福報！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>1</v>
-      </c>
       <c r="C83" t="n">
-        <v>0</v>
-      </c>
-      <c r="D83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
           <t>最强菩萨，地獄之主普渡眾生，20分鐘徹底了解地藏王菩薩。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
       <c r="C84" t="n">
-        <v>0</v>
-      </c>
-      <c r="D84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
           <t>最疼愛你的母親，竟是前世被你傷害過的人，佛陀開示因果輪回奧妙。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
       <c r="C85" t="n">
-        <v>0</v>
-      </c>
-      <c r="D85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
           <t>末法時代修行人必看，踏入這五種學佛誤區，只會讓佛菩薩越來越遠。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
       <c r="C86" t="n">
-        <v>0</v>
-      </c>
-      <c r="D86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
           <t>末法時代如何修行？釋迦牟尼開示阿難，這三種人最易圓滿！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
       <c r="C87" t="n">
-        <v>0</v>
-      </c>
-      <c r="D87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
           <t>末法時期如何修行？佛陀與藥師如來對話，揭示化解病苦的三大法門。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
       <c r="C88" t="n">
-        <v>0</v>
-      </c>
-      <c r="D88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>比丘問佛陀：色即是空，既然諸色皆空，為何修行之人要遠離女色。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
       <c r="C89" t="n">
-        <v>0</v>
-      </c>
-      <c r="D89" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D89" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>比丘問釋迦牟尼，何為眾生平等四相皆空，佛陀開示人同狗並無分別。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
       <c r="C90" t="n">
-        <v>0</v>
-      </c>
-      <c r="D90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>比丘尼問釋迦牟尼：女人為何難成佛？佛陀開示讓眾人豁然開朗。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
       <c r="C91" t="n">
-        <v>0</v>
-      </c>
-      <c r="D91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
           <t>波斯匿王問佛陀：為何布施越多福報越少，一個故事點破布施因果奧妙。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
       <c r="C92" t="n">
-        <v>0</v>
-      </c>
-      <c r="D92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D92" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>波斯匿迦問佛陀，「我」究竟是什麽？，佛陀開示無我觀的奧秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
       <c r="C93" t="n">
-        <v>0</v>
-      </c>
-      <c r="D93" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D93" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
           <t>涅槃寂靜，佛陀親授的終極解脫奧祕，一念之間超越生死。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
       <c r="C94" t="n">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D94" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>為什麼好人沒好報？高僧秘密開示：福報被“偷走”的3個徵兆！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>1</v>
-      </c>
       <c r="C95" t="n">
-        <v>0</v>
-      </c>
-      <c r="D95" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D95" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
           <t>為什麽佛說法四十九年，未曾說過一字？卻點亮無量眾生智慧，真相讓人驚嘆！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
       <c r="C96" t="n">
-        <v>0</v>
-      </c>
-      <c r="D96" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D96" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
           <t>為什麽佛陀說：持咒不如修心？一個漁夫的故事道破了修行的奥秘。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
       <c r="C97" t="n">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D97" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>為什麽說「十小咒」擁有無量功德？短短幾句就能往生極樂，祛病消災福慧雙增#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
       <c r="C98" t="n">
-        <v>0</v>
-      </c>
-      <c r="D98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D98" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
           <t>為何佛陀涅槃後，大迦葉與阿難爆發激烈爭執？竟藏著佛教分裂真相。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B99" t="n">
-        <v>1</v>
-      </c>
       <c r="C99" t="n">
-        <v>0</v>
-      </c>
-      <c r="D99" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D99" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
           <t>為何大德都說，2025年正月要誦讀金剛經？竟然蘊含著轉運玄機。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B100" t="n">
-        <v>1</v>
-      </c>
       <c r="C100" t="n">
-        <v>0</v>
-      </c>
-      <c r="D100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
           <t>為何高僧大德皆言，春節要讀地藏經？原來暗含這個修行機緣。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B101" t="n">
-        <v>1</v>
-      </c>
       <c r="C101" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D101" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
           <t>現今所說的四大皆空理念竟是錯誤的，這才是佛教「緣起論」的真正邏輯！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B102" t="n">
-        <v>1</v>
-      </c>
       <c r="C102" t="n">
-        <v>0</v>
-      </c>
-      <c r="D102" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D102" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>目犍連問佛陀：親人真的會在六道重逢嗎？佛陀的開示讓眾人淚目！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B103" t="n">
-        <v>1</v>
-      </c>
       <c r="C103" t="n">
-        <v>0</v>
-      </c>
-      <c r="D103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D103" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
           <t>目犍連示現五神通，佛陀告誡弟子，修行為解脫而非神通。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B104" t="n">
-        <v>1</v>
-      </c>
       <c r="C104" t="n">
-        <v>0</v>
-      </c>
-      <c r="D104" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D104" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>禪宗千年難題，執著與放下之間，如何找到菩提之路？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B105" t="n">
-        <v>1</v>
-      </c>
       <c r="C105" t="n">
-        <v>0</v>
-      </c>
-      <c r="D105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
           <t>維摩詰假病示疾，揭露「在家成佛」的五個陷阱！你踩中幾條？#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B106" t="n">
-        <v>1</v>
-      </c>
       <c r="C106" t="n">
-        <v>0</v>
-      </c>
-      <c r="D106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D106" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
           <t>維摩詰問佛陀：在家與出家修行有何不同？佛陀一語道破精進要訣。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B107" t="n">
-        <v>1</v>
-      </c>
       <c r="C107" t="n">
-        <v>0</v>
-      </c>
-      <c r="D107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
           <t>維摩詰問佛陀：生死之間究竟相隔多遠？佛陀用一片落葉揭示輪回。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B108" t="n">
-        <v>1</v>
-      </c>
       <c r="C108" t="n">
-        <v>0</v>
-      </c>
-      <c r="D108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D108" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
           <t>維摩詰開示弟子：做善事也會損耗福德，這四個標準才是行善關鍵。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B109" t="n">
-        <v>1</v>
-      </c>
       <c r="C109" t="n">
-        <v>0</v>
-      </c>
-      <c r="D109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D109" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
           <t>耆婆問釋迦牟尼：為何病人會痛苦？佛陀回答道出了生命真諦。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B110" t="n">
-        <v>1</v>
-      </c>
       <c r="C110" t="n">
-        <v>0</v>
-      </c>
-      <c r="D110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D110" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
           <t>舍利弗問釋迦牟尼：世尊您教導無住無執，為何又要世人皈依三寶。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B111" t="n">
-        <v>1</v>
-      </c>
       <c r="C111" t="n">
-        <v>0</v>
-      </c>
-      <c r="D111" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D111" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>虛空藏菩薩財富法，傳授五大富貴秘訣，第四訣改變命運軌跡。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B112" t="n">
-        <v>1</v>
-      </c>
       <c r="C112" t="n">
-        <v>0</v>
-      </c>
-      <c r="D112" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>西方極樂世界真的存在嗎？該如如何到達？原來也沒那麽難。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B113" t="n">
-        <v>1</v>
-      </c>
       <c r="C113" t="n">
-        <v>0</v>
-      </c>
-      <c r="D113" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D113" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
           <t>觀世音菩薩問佛陀：人死後真的會投胎嗎？佛陀的開示讓人徹悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B114" t="n">
-        <v>1</v>
-      </c>
       <c r="C114" t="n">
-        <v>0</v>
-      </c>
-      <c r="D114" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
           <t>觀世音菩薩開示：老天要渡化你，會給你五種提醒，要留意！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B115" t="n">
-        <v>1</v>
-      </c>
       <c r="C115" t="n">
-        <v>0</v>
-      </c>
-      <c r="D115" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
           <t>觀音菩薩開示：供奉佛像時四個禁忌，很多人不知道一直在犯。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B116" t="n">
-        <v>1</v>
-      </c>
       <c r="C116" t="n">
-        <v>0</v>
-      </c>
-      <c r="D116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>觀音菩薩開示：真正有慈悲之人，不是天天拜佛，而是具有這三種品性。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B117" t="n">
-        <v>1</v>
-      </c>
       <c r="C117" t="n">
-        <v>0</v>
-      </c>
-      <c r="D117" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>解讀《心經》，何爲“般若波羅蜜”，領悟佛法的終極智慧。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B118" t="n">
-        <v>1</v>
-      </c>
       <c r="C118" t="n">
-        <v>0</v>
-      </c>
-      <c r="D118" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
           <t>言多語失造口業，觀音菩薩開示：修習這三種口德可避災禍！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B119" t="n">
-        <v>1</v>
-      </c>
       <c r="C119" t="n">
-        <v>0</v>
-      </c>
-      <c r="D119" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
           <t>超度亡者時，是念「地藏經」，還是念「往生咒」，高僧開示區別很大。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B120" t="n">
-        <v>1</v>
-      </c>
       <c r="C120" t="n">
-        <v>0</v>
-      </c>
-      <c r="D120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
           <t>迦旃延問釋迦牟尼：世尊您教導無相，為何又要世人供養佛像。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B121" t="n">
-        <v>1</v>
-      </c>
       <c r="C121" t="n">
-        <v>0</v>
-      </c>
-      <c r="D121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>達摩祖師點化弟子：參禪難在求玄妙，悟得此道方為妙法。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B122" t="n">
-        <v>1</v>
-      </c>
       <c r="C122" t="n">
-        <v>0</v>
-      </c>
-      <c r="D122" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>釋迦牟尼佛為何斷言人生皆苦？十分鐘講透佛教四聖諦真相#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B123" t="n">
-        <v>1</v>
-      </c>
       <c r="C123" t="n">
-        <v>0</v>
-      </c>
-      <c r="D123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
           <t>釋迦牟尼：真正開悟的人都會具有這三種狀態。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B124" t="n">
-        <v>1</v>
-      </c>
       <c r="C124" t="n">
-        <v>0</v>
-      </c>
-      <c r="D124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
           <t>阿難問佛陀：人心如何才能不散亂？佛陀指出了日常生活中的修行法。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B125" t="n">
-        <v>1</v>
-      </c>
       <c r="C125" t="n">
-        <v>0</v>
-      </c>
-      <c r="D125" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
           <t>阿難問佛陀：面對災禍，佛菩薩為何不普渡眾生，原來這兩種情況無法救度。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B126" t="n">
-        <v>1</v>
-      </c>
       <c r="C126" t="n">
-        <v>0</v>
-      </c>
-      <c r="D126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼佛：涅槃是新生還是他生？佛陀回答讓眾生頓悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B127" t="n">
-        <v>1</v>
-      </c>
       <c r="C127" t="n">
-        <v>0</v>
-      </c>
-      <c r="D127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼，如何區分真假開悟，佛陀用四句話讓眾人徹悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B128" t="n">
-        <v>1</v>
-      </c>
       <c r="C128" t="n">
-        <v>0</v>
-      </c>
-      <c r="D128" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：世尊為何不開創凈土？佛陀的回答讓人頓悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B129" t="n">
-        <v>1</v>
-      </c>
       <c r="C129" t="n">
-        <v>0</v>
-      </c>
-      <c r="D129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：人為何會有生死？佛陀回答道出生死真相。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B130" t="n">
-        <v>1</v>
-      </c>
       <c r="C130" t="n">
-        <v>0</v>
-      </c>
-      <c r="D130" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：您涅槃之後還會輪回嗎？佛陀的回答令眾生頓悟。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B131" t="n">
-        <v>1</v>
-      </c>
       <c r="C131" t="n">
-        <v>0</v>
-      </c>
-      <c r="D131" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>阿難問釋迦牟尼：為何修行越深心魔越強？佛陀指出了關鍵盲點！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B132" t="n">
-        <v>1</v>
-      </c>
       <c r="C132" t="n">
-        <v>0</v>
-      </c>
-      <c r="D132" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
           <t>阿難問：世尊教導不執著，為何對佛法如此珍重？佛陀回答令人深思。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B133" t="n">
-        <v>1</v>
-      </c>
       <c r="C133" t="n">
-        <v>0</v>
-      </c>
-      <c r="D133" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
           <t>阿難尊者親歷，觀世音菩薩顯靈傳授，讓祈求必成的三個發願法則！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B134" t="n">
-        <v>1</v>
-      </c>
       <c r="C134" t="n">
-        <v>0</v>
-      </c>
-      <c r="D134" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>阿難開示比丘，心淫比身淫更傷修行，領悟此法可助斷欲修身。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B135" t="n">
-        <v>1</v>
-      </c>
       <c r="C135" t="n">
-        <v>0</v>
-      </c>
-      <c r="D135" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
           <t>隨喜加入，同修善法，南無阿彌陀佛！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B136" t="n">
-        <v>1</v>
-      </c>
       <c r="C136" t="n">
-        <v>0</v>
-      </c>
-      <c r="D136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
           <t>須菩提問佛陀，什麽是「無生法忍」，文殊菩薩道破修行終極奧義。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B137" t="n">
-        <v>1</v>
-      </c>
       <c r="C137" t="n">
-        <v>0</v>
-      </c>
-      <c r="D137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
           <t>須菩提問佛陀：世間苦難何時了？佛陀妙語開示眾人醒悟！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B138" t="n">
-        <v>1</v>
-      </c>
       <c r="C138" t="n">
-        <v>0</v>
-      </c>
-      <c r="D138" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
           <t>須達多問佛陀：為何好人早逝，惡人長壽，一個故事揭開三世因果真相。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B139" t="n">
-        <v>1</v>
-      </c>
       <c r="C139" t="n">
-        <v>0</v>
-      </c>
-      <c r="D139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
           <t>須達多問釋迦牟尼：佛陀您教導布施，為何還要弟子日日托缽。#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B140" t="n">
-        <v>1</v>
-      </c>
       <c r="C140" t="n">
-        <v>0</v>
-      </c>
-      <c r="D140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
           <t>颠覆你对佛法的认知！99%的人都误解的修行真相，佛教真正的秘密首次揭露！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B141" t="n">
-        <v>1</v>
-      </c>
       <c r="C141" t="n">
-        <v>0</v>
-      </c>
-      <c r="D141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
           <t>體內住著兩個“自己”？佛陀：識得“元神”，方能跳出輪迴！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B142" t="n">
-        <v>1</v>
-      </c>
       <c r="C142" t="n">
-        <v>0</v>
-      </c>
-      <c r="D142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>佛道禪緣</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
           <t>鬼怕哪種人？佛說：有3種人，連鬼也不敢靠近他！#佛教 #佛家 #佛法 #佛學知識 #佛學智慧 #修心修行 #佛教文化 #禪悟人生 #傳統文化.mp4</t>
         </is>
       </c>
-      <c r="B143" t="n">
-        <v>1</v>
-      </c>
       <c r="C143" t="n">
-        <v>0</v>
-      </c>
-      <c r="D143" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -2,26 +2,176 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ko" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="22">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -30,20 +180,319 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="11">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -53,17 +502,212 @@
       <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -416,7 +1060,6 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -430,27 +1073,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>频道名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>MP4名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>是否发布</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>是否已经发布</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -475,7 +1118,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2025-06-02 06:02:03</t>
+          <t>2025-06-03 04:38:33</t>
         </is>
       </c>
     </row>
@@ -494,9 +1137,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-06-03 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -513,9 +1160,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-06-03 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -532,9 +1183,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-06-03 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -551,9 +1206,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-06-04 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -570,9 +1229,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-06-04 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -589,9 +1252,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -608,9 +1275,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-06-04 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -627,9 +1298,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -646,9 +1321,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-06-05 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -665,9 +1344,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-06-05 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -684,9 +1367,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-06-05 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -722,9 +1409,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-06-06 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -741,9 +1432,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-06-06 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -760,9 +1455,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-06-06 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -779,9 +1478,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-06-06 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -798,9 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-06-07 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -817,9 +1524,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-06-07 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -836,9 +1547,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-06-07 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -874,9 +1589,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-06-07 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -931,7 +1650,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
@@ -950,7 +1669,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E27" t="inlineStr"/>
     </row>
@@ -969,7 +1688,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
@@ -1045,7 +1764,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E32" t="inlineStr"/>
     </row>
@@ -1140,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
@@ -1178,7 +1897,7 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" t="inlineStr"/>
     </row>
@@ -1216,7 +1935,7 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" t="inlineStr"/>
     </row>
@@ -1330,7 +2049,7 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E47" t="inlineStr"/>
     </row>
@@ -1349,7 +2068,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E48" t="inlineStr"/>
     </row>
@@ -1539,7 +2258,7 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E58" t="inlineStr"/>
     </row>
@@ -1976,7 +2695,7 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E81" t="inlineStr"/>
     </row>
@@ -2052,7 +2771,7 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E85" t="inlineStr"/>
     </row>
@@ -2185,7 +2904,7 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E92" t="inlineStr"/>
     </row>
@@ -2204,7 +2923,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E93" t="inlineStr"/>
     </row>
@@ -2565,7 +3284,7 @@
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E112" t="inlineStr"/>
     </row>
@@ -2660,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E117" t="inlineStr"/>
     </row>
@@ -2831,7 +3550,7 @@
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E126" t="inlineStr"/>
     </row>
@@ -2945,7 +3664,7 @@
         <v>1</v>
       </c>
       <c r="D132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E132" t="inlineStr"/>
     </row>
@@ -3002,7 +3721,7 @@
         <v>1</v>
       </c>
       <c r="D135" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E135" t="inlineStr"/>
     </row>
@@ -3021,7 +3740,7 @@
         <v>1</v>
       </c>
       <c r="D136" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
@@ -3132,7 +3851,10 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E143"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <cols>
+    <col width="54.3269230769231" customWidth="1" min="2" max="2"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -3608,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -3626,7 +4348,7 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -3644,7 +4366,7 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3716,7 +4438,7 @@
         <v>1</v>
       </c>
       <c r="D32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -3788,7 +4510,7 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -3860,7 +4582,7 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -3896,7 +4618,7 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -4004,7 +4726,7 @@
         <v>1</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -4022,7 +4744,7 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -4202,7 +4924,7 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -4616,7 +5338,7 @@
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="83">
@@ -4688,7 +5410,7 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="87">
@@ -4814,7 +5536,7 @@
         <v>1</v>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="94">
@@ -4832,7 +5554,7 @@
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="95">
@@ -5153,7 +5875,7 @@
         </is>
       </c>
       <c r="C112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
         <v>0</v>
@@ -5174,7 +5896,7 @@
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="114">
@@ -5246,7 +5968,7 @@
         <v>1</v>
       </c>
       <c r="D117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="118">
@@ -5444,7 +6166,7 @@
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="129">
@@ -5552,7 +6274,7 @@
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="135">
@@ -5606,7 +6328,7 @@
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="138">
@@ -5624,7 +6346,7 @@
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="139">

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="31360" windowHeight="16360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" state="visible" r:id="rId1"/>
@@ -1141,7 +1141,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-06-03 10:38:33</t>
+          <t>2025-06-12 22:38:33</t>
         </is>
       </c>
     </row>
@@ -1164,7 +1164,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-06-03 16:38:33</t>
+          <t>2025-06-13 04:38:33</t>
         </is>
       </c>
     </row>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-06-03 22:38:33</t>
+          <t>2025-06-13 10:38:33</t>
         </is>
       </c>
     </row>
@@ -1390,9 +1390,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-06-08 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1570,9 +1574,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-06-08 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1612,9 +1620,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-06-08 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1631,9 +1643,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-06-08 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1652,7 +1668,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1671,7 +1686,6 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1690,7 +1704,6 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1707,9 +1720,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-06-09 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1726,9 +1743,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-06-09 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1745,9 +1766,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-06-09 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1766,7 +1791,6 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1783,9 +1807,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-06-13 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1802,9 +1830,13 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-06-09 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1821,9 +1853,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-06-10 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1840,9 +1876,8 @@
         <v>1</v>
       </c>
       <c r="D36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E36" t="inlineStr"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1861,7 +1896,6 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
-      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1878,9 +1912,8 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>1</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1899,7 +1932,6 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
-      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1916,9 +1948,13 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-06-10 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1937,7 +1973,6 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
-      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1954,9 +1989,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-06-10 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1973,9 +2012,13 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1992,9 +2035,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-06-13 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2011,9 +2058,13 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-06-11 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2030,9 +2081,13 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2051,7 +2106,6 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
-      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2070,7 +2124,6 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2087,9 +2140,13 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-06-11 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2106,9 +2163,13 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-06-14 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2125,9 +2186,13 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2144,9 +2209,13 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-06-14 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2163,9 +2232,13 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-06-12 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2182,9 +2255,13 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-06-12 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2201,9 +2278,13 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-06-14 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2220,9 +2301,13 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-06-14 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2239,9 +2324,13 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-06-15 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2260,7 +2349,6 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
-      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2277,9 +2365,13 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025-06-12 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2296,9 +2388,13 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-06-15 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2315,9 +2411,13 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-06-15 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2334,9 +2434,13 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-06-15 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2353,9 +2457,13 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-06-16 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2372,9 +2480,13 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-06-16 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2391,9 +2503,13 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-06-16 16:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2410,9 +2526,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-06-16 22:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2429,9 +2549,13 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-06-17 04:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2448,9 +2572,13 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-06-17 10:38:33</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2469,7 +2597,6 @@
       <c r="D69" t="n">
         <v>0</v>
       </c>
-      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2488,7 +2615,6 @@
       <c r="D70" t="n">
         <v>0</v>
       </c>
-      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2507,7 +2633,6 @@
       <c r="D71" t="n">
         <v>0</v>
       </c>
-      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2526,7 +2651,6 @@
       <c r="D72" t="n">
         <v>0</v>
       </c>
-      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2545,7 +2669,6 @@
       <c r="D73" t="n">
         <v>0</v>
       </c>
-      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2564,7 +2687,6 @@
       <c r="D74" t="n">
         <v>0</v>
       </c>
-      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2583,7 +2705,6 @@
       <c r="D75" t="n">
         <v>0</v>
       </c>
-      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2602,7 +2723,6 @@
       <c r="D76" t="n">
         <v>0</v>
       </c>
-      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2621,7 +2741,6 @@
       <c r="D77" t="n">
         <v>0</v>
       </c>
-      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2640,7 +2759,6 @@
       <c r="D78" t="n">
         <v>0</v>
       </c>
-      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2659,7 +2777,6 @@
       <c r="D79" t="n">
         <v>0</v>
       </c>
-      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2678,7 +2795,6 @@
       <c r="D80" t="n">
         <v>0</v>
       </c>
-      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2697,7 +2813,6 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
-      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2716,7 +2831,6 @@
       <c r="D82" t="n">
         <v>0</v>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2735,7 +2849,6 @@
       <c r="D83" t="n">
         <v>0</v>
       </c>
-      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2754,7 +2867,6 @@
       <c r="D84" t="n">
         <v>0</v>
       </c>
-      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2773,7 +2885,6 @@
       <c r="D85" t="n">
         <v>1</v>
       </c>
-      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2792,7 +2903,6 @@
       <c r="D86" t="n">
         <v>0</v>
       </c>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2811,7 +2921,6 @@
       <c r="D87" t="n">
         <v>0</v>
       </c>
-      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2830,7 +2939,6 @@
       <c r="D88" t="n">
         <v>0</v>
       </c>
-      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2849,7 +2957,6 @@
       <c r="D89" t="n">
         <v>0</v>
       </c>
-      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2868,7 +2975,6 @@
       <c r="D90" t="n">
         <v>0</v>
       </c>
-      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2887,7 +2993,6 @@
       <c r="D91" t="n">
         <v>0</v>
       </c>
-      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2906,7 +3011,6 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
-      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2925,7 +3029,6 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2944,7 +3047,6 @@
       <c r="D94" t="n">
         <v>0</v>
       </c>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2963,7 +3065,6 @@
       <c r="D95" t="n">
         <v>0</v>
       </c>
-      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2982,7 +3083,6 @@
       <c r="D96" t="n">
         <v>0</v>
       </c>
-      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3001,7 +3101,6 @@
       <c r="D97" t="n">
         <v>0</v>
       </c>
-      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3020,7 +3119,6 @@
       <c r="D98" t="n">
         <v>0</v>
       </c>
-      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3039,7 +3137,6 @@
       <c r="D99" t="n">
         <v>0</v>
       </c>
-      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3058,7 +3155,6 @@
       <c r="D100" t="n">
         <v>0</v>
       </c>
-      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3077,7 +3173,6 @@
       <c r="D101" t="n">
         <v>0</v>
       </c>
-      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3096,7 +3191,6 @@
       <c r="D102" t="n">
         <v>0</v>
       </c>
-      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3115,7 +3209,6 @@
       <c r="D103" t="n">
         <v>0</v>
       </c>
-      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3134,7 +3227,6 @@
       <c r="D104" t="n">
         <v>0</v>
       </c>
-      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3153,7 +3245,6 @@
       <c r="D105" t="n">
         <v>0</v>
       </c>
-      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3172,7 +3263,6 @@
       <c r="D106" t="n">
         <v>0</v>
       </c>
-      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3191,7 +3281,6 @@
       <c r="D107" t="n">
         <v>0</v>
       </c>
-      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3210,7 +3299,6 @@
       <c r="D108" t="n">
         <v>0</v>
       </c>
-      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3229,7 +3317,6 @@
       <c r="D109" t="n">
         <v>0</v>
       </c>
-      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3248,7 +3335,6 @@
       <c r="D110" t="n">
         <v>0</v>
       </c>
-      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3267,7 +3353,6 @@
       <c r="D111" t="n">
         <v>0</v>
       </c>
-      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3286,7 +3371,6 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
-      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3305,7 +3389,6 @@
       <c r="D113" t="n">
         <v>0</v>
       </c>
-      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3324,7 +3407,6 @@
       <c r="D114" t="n">
         <v>0</v>
       </c>
-      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3343,7 +3425,6 @@
       <c r="D115" t="n">
         <v>0</v>
       </c>
-      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3362,7 +3443,6 @@
       <c r="D116" t="n">
         <v>0</v>
       </c>
-      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3381,7 +3461,6 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3400,7 +3479,6 @@
       <c r="D118" t="n">
         <v>0</v>
       </c>
-      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3419,7 +3497,6 @@
       <c r="D119" t="n">
         <v>0</v>
       </c>
-      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3438,7 +3515,6 @@
       <c r="D120" t="n">
         <v>0</v>
       </c>
-      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3457,7 +3533,6 @@
       <c r="D121" t="n">
         <v>0</v>
       </c>
-      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3476,7 +3551,6 @@
       <c r="D122" t="n">
         <v>0</v>
       </c>
-      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3495,7 +3569,6 @@
       <c r="D123" t="n">
         <v>0</v>
       </c>
-      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3514,7 +3587,6 @@
       <c r="D124" t="n">
         <v>0</v>
       </c>
-      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3533,7 +3605,6 @@
       <c r="D125" t="n">
         <v>0</v>
       </c>
-      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3552,7 +3623,6 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
-      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3571,7 +3641,6 @@
       <c r="D127" t="n">
         <v>0</v>
       </c>
-      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3590,7 +3659,6 @@
       <c r="D128" t="n">
         <v>0</v>
       </c>
-      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3609,7 +3677,6 @@
       <c r="D129" t="n">
         <v>0</v>
       </c>
-      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3628,7 +3695,6 @@
       <c r="D130" t="n">
         <v>0</v>
       </c>
-      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3647,7 +3713,6 @@
       <c r="D131" t="n">
         <v>0</v>
       </c>
-      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3666,7 +3731,6 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
-      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3685,7 +3749,6 @@
       <c r="D133" t="n">
         <v>0</v>
       </c>
-      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3704,7 +3767,6 @@
       <c r="D134" t="n">
         <v>0</v>
       </c>
-      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3723,7 +3785,6 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
-      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3742,7 +3803,6 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
-      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3761,7 +3821,6 @@
       <c r="D137" t="n">
         <v>0</v>
       </c>
-      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3780,7 +3839,6 @@
       <c r="D138" t="n">
         <v>0</v>
       </c>
-      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3799,7 +3857,6 @@
       <c r="D139" t="n">
         <v>0</v>
       </c>
-      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3818,7 +3875,6 @@
       <c r="D140" t="n">
         <v>0</v>
       </c>
-      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3837,7 +3893,6 @@
       <c r="D141" t="n">
         <v>0</v>
       </c>
-      <c r="E141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3851,33 +3906,30 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E143"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
-  <cols>
-    <col width="54.3269230769231" customWidth="1" min="2" max="2"/>
-  </cols>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>频道名称</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>MP4名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>是否发布</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>是否已经发布</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -3898,7 +3950,12 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2025-06-03 22:55:22</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -3916,7 +3973,12 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2025-06-04 04:55:22</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -3934,7 +3996,12 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2025-06-04 10:55:22</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -3952,7 +4019,12 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>2025-06-04 16:55:22</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -3970,7 +4042,12 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>2025-06-04 22:55:22</t>
+        </is>
       </c>
     </row>
     <row r="7">
@@ -3988,7 +4065,12 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>2025-06-05 22:55:22</t>
+        </is>
       </c>
     </row>
     <row r="8">
@@ -4006,7 +4088,12 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>2025-06-05 04:55:22</t>
+        </is>
       </c>
     </row>
     <row r="9">
@@ -4024,7 +4111,12 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>2025-06-05 10:55:22</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -4042,7 +4134,12 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>2025-06-05 16:55:22</t>
+        </is>
       </c>
     </row>
     <row r="11">
@@ -4060,7 +4157,12 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>2025-06-06 04:55:22</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -4078,7 +4180,12 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>2025-06-06 10:55:22</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -4096,7 +4203,12 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-06-06 16:55:22</t>
+        </is>
       </c>
     </row>
     <row r="14">
@@ -4114,7 +4226,12 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-06-06 22:55:22</t>
+        </is>
       </c>
     </row>
     <row r="15">
@@ -4134,6 +4251,7 @@
       <c r="D15" t="n">
         <v>0</v>
       </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4152,6 +4270,7 @@
       <c r="D16" t="n">
         <v>0</v>
       </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4170,6 +4289,7 @@
       <c r="D17" t="n">
         <v>0</v>
       </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4188,6 +4308,7 @@
       <c r="D18" t="n">
         <v>0</v>
       </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4206,6 +4327,7 @@
       <c r="D19" t="n">
         <v>0</v>
       </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4224,6 +4346,7 @@
       <c r="D20" t="n">
         <v>0</v>
       </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4242,6 +4365,7 @@
       <c r="D21" t="n">
         <v>0</v>
       </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4260,6 +4384,7 @@
       <c r="D22" t="n">
         <v>0</v>
       </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4278,6 +4403,7 @@
       <c r="D23" t="n">
         <v>0</v>
       </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4296,6 +4422,7 @@
       <c r="D24" t="n">
         <v>0</v>
       </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4314,6 +4441,7 @@
       <c r="D25" t="n">
         <v>0</v>
       </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4332,6 +4460,7 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4350,6 +4479,7 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -4368,6 +4498,7 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -4386,6 +4517,7 @@
       <c r="D29" t="n">
         <v>0</v>
       </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4404,6 +4536,7 @@
       <c r="D30" t="n">
         <v>0</v>
       </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4422,6 +4555,7 @@
       <c r="D31" t="n">
         <v>0</v>
       </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4440,6 +4574,7 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -4458,6 +4593,7 @@
       <c r="D33" t="n">
         <v>0</v>
       </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4476,6 +4612,7 @@
       <c r="D34" t="n">
         <v>0</v>
       </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4494,6 +4631,7 @@
       <c r="D35" t="n">
         <v>0</v>
       </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4512,6 +4650,7 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -4530,6 +4669,7 @@
       <c r="D37" t="n">
         <v>0</v>
       </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4548,6 +4688,7 @@
       <c r="D38" t="n">
         <v>0</v>
       </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4566,6 +4707,7 @@
       <c r="D39" t="n">
         <v>0</v>
       </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4584,6 +4726,7 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -4602,6 +4745,7 @@
       <c r="D41" t="n">
         <v>0</v>
       </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4620,6 +4764,7 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4638,6 +4783,7 @@
       <c r="D43" t="n">
         <v>0</v>
       </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4656,6 +4802,7 @@
       <c r="D44" t="n">
         <v>0</v>
       </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4674,6 +4821,7 @@
       <c r="D45" t="n">
         <v>0</v>
       </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4692,6 +4840,7 @@
       <c r="D46" t="n">
         <v>0</v>
       </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4710,6 +4859,7 @@
       <c r="D47" t="n">
         <v>0</v>
       </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4728,6 +4878,7 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4746,6 +4897,7 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4764,6 +4916,7 @@
       <c r="D50" t="n">
         <v>0</v>
       </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4782,6 +4935,7 @@
       <c r="D51" t="n">
         <v>0</v>
       </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4800,6 +4954,7 @@
       <c r="D52" t="n">
         <v>0</v>
       </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4818,6 +4973,7 @@
       <c r="D53" t="n">
         <v>0</v>
       </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4836,6 +4992,7 @@
       <c r="D54" t="n">
         <v>0</v>
       </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4854,6 +5011,7 @@
       <c r="D55" t="n">
         <v>0</v>
       </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4872,6 +5030,7 @@
       <c r="D56" t="n">
         <v>0</v>
       </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4890,6 +5049,7 @@
       <c r="D57" t="n">
         <v>0</v>
       </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4908,6 +5068,7 @@
       <c r="D58" t="n">
         <v>0</v>
       </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4926,6 +5087,7 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4944,6 +5106,7 @@
       <c r="D60" t="n">
         <v>0</v>
       </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4962,6 +5125,7 @@
       <c r="D61" t="n">
         <v>0</v>
       </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4980,6 +5144,7 @@
       <c r="D62" t="n">
         <v>0</v>
       </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4998,6 +5163,7 @@
       <c r="D63" t="n">
         <v>0</v>
       </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5016,6 +5182,7 @@
       <c r="D64" t="n">
         <v>0</v>
       </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5034,6 +5201,7 @@
       <c r="D65" t="n">
         <v>0</v>
       </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5052,6 +5220,7 @@
       <c r="D66" t="n">
         <v>0</v>
       </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5070,6 +5239,7 @@
       <c r="D67" t="n">
         <v>0</v>
       </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5088,6 +5258,7 @@
       <c r="D68" t="n">
         <v>0</v>
       </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5106,6 +5277,7 @@
       <c r="D69" t="n">
         <v>0</v>
       </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5124,6 +5296,7 @@
       <c r="D70" t="n">
         <v>0</v>
       </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5142,6 +5315,7 @@
       <c r="D71" t="n">
         <v>0</v>
       </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5160,6 +5334,7 @@
       <c r="D72" t="n">
         <v>0</v>
       </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5178,6 +5353,7 @@
       <c r="D73" t="n">
         <v>0</v>
       </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5196,6 +5372,7 @@
       <c r="D74" t="n">
         <v>0</v>
       </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5214,6 +5391,7 @@
       <c r="D75" t="n">
         <v>0</v>
       </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5232,6 +5410,7 @@
       <c r="D76" t="n">
         <v>0</v>
       </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5250,6 +5429,7 @@
       <c r="D77" t="n">
         <v>0</v>
       </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5268,6 +5448,7 @@
       <c r="D78" t="n">
         <v>0</v>
       </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5286,6 +5467,7 @@
       <c r="D79" t="n">
         <v>0</v>
       </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5304,6 +5486,7 @@
       <c r="D80" t="n">
         <v>0</v>
       </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5322,6 +5505,7 @@
       <c r="D81" t="n">
         <v>0</v>
       </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5340,6 +5524,7 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5358,6 +5543,7 @@
       <c r="D83" t="n">
         <v>0</v>
       </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5376,6 +5562,7 @@
       <c r="D84" t="n">
         <v>0</v>
       </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5394,6 +5581,7 @@
       <c r="D85" t="n">
         <v>0</v>
       </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5412,6 +5600,7 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5430,6 +5619,7 @@
       <c r="D87" t="n">
         <v>0</v>
       </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5448,6 +5638,7 @@
       <c r="D88" t="n">
         <v>0</v>
       </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5466,6 +5657,7 @@
       <c r="D89" t="n">
         <v>0</v>
       </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5484,6 +5676,7 @@
       <c r="D90" t="n">
         <v>0</v>
       </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5502,6 +5695,7 @@
       <c r="D91" t="n">
         <v>0</v>
       </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5520,6 +5714,7 @@
       <c r="D92" t="n">
         <v>0</v>
       </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5538,6 +5733,7 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5556,6 +5752,7 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5574,6 +5771,7 @@
       <c r="D95" t="n">
         <v>0</v>
       </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5592,6 +5790,7 @@
       <c r="D96" t="n">
         <v>0</v>
       </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5610,6 +5809,7 @@
       <c r="D97" t="n">
         <v>0</v>
       </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5628,6 +5828,7 @@
       <c r="D98" t="n">
         <v>0</v>
       </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5646,6 +5847,7 @@
       <c r="D99" t="n">
         <v>0</v>
       </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5664,6 +5866,7 @@
       <c r="D100" t="n">
         <v>0</v>
       </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5682,6 +5885,7 @@
       <c r="D101" t="n">
         <v>0</v>
       </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5700,6 +5904,7 @@
       <c r="D102" t="n">
         <v>0</v>
       </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5718,6 +5923,7 @@
       <c r="D103" t="n">
         <v>0</v>
       </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5736,6 +5942,7 @@
       <c r="D104" t="n">
         <v>0</v>
       </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5754,6 +5961,7 @@
       <c r="D105" t="n">
         <v>0</v>
       </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5772,6 +5980,7 @@
       <c r="D106" t="n">
         <v>0</v>
       </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5790,6 +5999,7 @@
       <c r="D107" t="n">
         <v>0</v>
       </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5808,6 +6018,7 @@
       <c r="D108" t="n">
         <v>0</v>
       </c>
+      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5826,6 +6037,7 @@
       <c r="D109" t="n">
         <v>0</v>
       </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5844,6 +6056,7 @@
       <c r="D110" t="n">
         <v>0</v>
       </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5862,6 +6075,7 @@
       <c r="D111" t="n">
         <v>0</v>
       </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5880,6 +6094,7 @@
       <c r="D112" t="n">
         <v>0</v>
       </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5898,6 +6113,7 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5916,6 +6132,7 @@
       <c r="D114" t="n">
         <v>0</v>
       </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5934,6 +6151,7 @@
       <c r="D115" t="n">
         <v>0</v>
       </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5952,6 +6170,7 @@
       <c r="D116" t="n">
         <v>0</v>
       </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5970,6 +6189,7 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5988,6 +6208,7 @@
       <c r="D118" t="n">
         <v>0</v>
       </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6006,6 +6227,7 @@
       <c r="D119" t="n">
         <v>0</v>
       </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6024,6 +6246,7 @@
       <c r="D120" t="n">
         <v>0</v>
       </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6042,6 +6265,7 @@
       <c r="D121" t="n">
         <v>0</v>
       </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6060,6 +6284,7 @@
       <c r="D122" t="n">
         <v>0</v>
       </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6078,6 +6303,7 @@
       <c r="D123" t="n">
         <v>0</v>
       </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6096,6 +6322,7 @@
       <c r="D124" t="n">
         <v>0</v>
       </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6114,6 +6341,7 @@
       <c r="D125" t="n">
         <v>0</v>
       </c>
+      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6132,6 +6360,7 @@
       <c r="D126" t="n">
         <v>0</v>
       </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6150,6 +6379,7 @@
       <c r="D127" t="n">
         <v>0</v>
       </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -6168,6 +6398,7 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -6186,6 +6417,7 @@
       <c r="D129" t="n">
         <v>0</v>
       </c>
+      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -6204,6 +6436,7 @@
       <c r="D130" t="n">
         <v>0</v>
       </c>
+      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -6222,6 +6455,7 @@
       <c r="D131" t="n">
         <v>0</v>
       </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -6240,6 +6474,7 @@
       <c r="D132" t="n">
         <v>0</v>
       </c>
+      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -6258,6 +6493,7 @@
       <c r="D133" t="n">
         <v>0</v>
       </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -6276,6 +6512,7 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
+      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -6294,6 +6531,7 @@
       <c r="D135" t="n">
         <v>0</v>
       </c>
+      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -6312,6 +6550,7 @@
       <c r="D136" t="n">
         <v>0</v>
       </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -6330,6 +6569,7 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -6348,6 +6588,7 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
+      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -6366,6 +6607,7 @@
       <c r="D139" t="n">
         <v>0</v>
       </c>
+      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -6384,6 +6626,7 @@
       <c r="D140" t="n">
         <v>0</v>
       </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -6402,6 +6645,7 @@
       <c r="D141" t="n">
         <v>0</v>
       </c>
+      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -6420,6 +6664,7 @@
       <c r="D142" t="n">
         <v>0</v>
       </c>
+      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -6438,6 +6683,7 @@
       <c r="D143" t="n">
         <v>0</v>
       </c>
+      <c r="E143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -4249,9 +4249,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-06-07 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4268,9 +4272,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-06-07 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4287,9 +4295,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-06-07 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4306,9 +4318,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-06-07 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4325,9 +4341,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-06-08 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4344,9 +4364,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-06-08 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4363,9 +4387,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-06-08 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4382,9 +4410,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-06-08 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4401,9 +4433,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-06-09 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4420,9 +4456,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-06-09 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4439,9 +4479,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-06-09 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4515,9 +4559,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-06-09 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4534,9 +4582,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-06-10 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="31360" windowHeight="16360" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="31360" windowHeight="16360" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" state="visible" r:id="rId1"/>
@@ -1070,30 +1070,30 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E141"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>频道名称</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>MP4名称</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>是否发布</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>是否已经发布</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -4605,9 +4605,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-06-10 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4643,9 +4647,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-06-10 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4662,9 +4670,13 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4681,9 +4693,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-06-11 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4719,9 +4735,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4738,9 +4758,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-06-11 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4757,9 +4781,13 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4795,9 +4823,13 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-06-12 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4833,9 +4865,13 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-06-12 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4852,9 +4888,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-06-12 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4871,9 +4911,13 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-06-12 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4890,9 +4934,13 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-06-13 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4909,9 +4957,13 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025-06-13 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4966,9 +5018,13 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-06-13 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4985,9 +5041,13 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-06-13 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5004,9 +5064,13 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-06-14 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5023,9 +5087,13 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-06-14 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5042,9 +5110,13 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-06-14 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5061,9 +5133,13 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-06-14 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5080,9 +5156,13 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-06-15 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5099,9 +5179,13 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-06-15 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5118,9 +5202,13 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-06-15 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5156,9 +5244,13 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-06-15 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5175,9 +5267,13 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-06-16 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5194,9 +5290,13 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-06-16 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5213,9 +5313,13 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-06-16 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5232,9 +5336,13 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-06-16 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5251,9 +5359,13 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-06-17 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5270,9 +5382,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-06-17 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5289,9 +5405,13 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-06-17 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5308,9 +5428,13 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-06-17 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5327,9 +5451,13 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2025-06-18 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5346,9 +5474,13 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025-06-18 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5365,9 +5497,13 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2025-06-18 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5384,9 +5520,13 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025-06-18 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5403,9 +5543,13 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2025-06-19 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5422,9 +5566,13 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2025-06-19 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5441,9 +5589,13 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-06-19 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5460,9 +5612,13 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2025-06-19 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5479,9 +5635,13 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2025-06-20 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5498,9 +5658,13 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2025-06-20 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5517,9 +5681,13 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2025-06-20 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5536,9 +5704,13 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2025-06-20 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5555,9 +5727,13 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2025-06-21 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5593,9 +5769,13 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2025-06-21 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5612,9 +5792,13 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2025-06-21 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5631,9 +5815,13 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2025-06-21 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5669,9 +5857,13 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2025-06-22 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5688,9 +5880,13 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2025-06-22 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5707,9 +5903,13 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2025-06-22 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5726,9 +5926,13 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2025-06-22 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5745,9 +5949,13 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2025-06-23 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5764,9 +5972,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2025-06-23 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5821,9 +6033,13 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2025-06-23 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5859,9 +6075,13 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2025-06-23 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5878,9 +6098,13 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2025-06-24 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5897,9 +6121,13 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2025-06-24 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5916,9 +6144,13 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2025-06-24 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5935,9 +6167,13 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2025-06-24 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5954,9 +6190,13 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2025-06-25 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5973,9 +6213,13 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2025-06-25 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5992,9 +6236,13 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2025-06-25 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6011,9 +6259,13 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2025-06-25 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6030,9 +6282,13 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2025-06-26 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6049,9 +6305,13 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2025-06-26 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6068,9 +6328,13 @@
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2025-06-26 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6087,9 +6351,13 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2025-06-26 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6106,9 +6374,13 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2025-06-27 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6125,9 +6397,13 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2025-06-27 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6182,9 +6458,13 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2025-06-27 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6201,9 +6481,13 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2025-06-27 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6220,9 +6504,13 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2025-06-28 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6258,9 +6546,13 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2025-06-28 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6277,9 +6569,13 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2025-06-28 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6296,9 +6592,13 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2025-06-28 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6315,9 +6615,13 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2025-06-29 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6334,9 +6638,13 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2025-06-29 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6353,9 +6661,13 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2025-06-29 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6372,9 +6684,13 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2025-06-29 22:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6391,9 +6707,13 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2025-06-30 04:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6410,9 +6730,13 @@
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>0</v>
-      </c>
-      <c r="E126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>2025-06-30 10:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6429,9 +6753,13 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2025-06-30 16:55:22</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -2,176 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="31360" windowHeight="16360" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="en" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="ko" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="191029" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="22">
+  <fonts count="2">
     <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF0000FF"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF800080"/>
-      <sz val="11"/>
-      <u val="single"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="18"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <i val="1"/>
-      <color rgb="FF7F7F7F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="15"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="13"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <b val="1"/>
-      <color theme="3"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF3F3F76"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FF3F3F3F"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FFFA7D00"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <b val="1"/>
-      <color theme="1"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF006100"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C0006"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color rgb="FF9C6500"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <color theme="0"/>
-      <sz val="11"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
@@ -180,319 +30,20 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -502,212 +53,17 @@
       <bottom style="thin"/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -1060,6 +416,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -1070,7 +427,7 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:E141"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
@@ -1367,13 +724,9 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2025-06-05 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1390,13 +743,9 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2025-06-08 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1413,13 +762,9 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2025-06-06 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1436,13 +781,9 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2025-06-06 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1459,13 +800,9 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2025-06-06 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1482,13 +819,9 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2025-06-06 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1505,13 +838,9 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2025-06-07 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1528,13 +857,9 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2025-06-07 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1551,13 +876,9 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2025-06-07 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1574,13 +895,9 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2025-06-08 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1597,13 +914,9 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2025-06-07 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1620,13 +933,9 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2025-06-08 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1643,13 +952,9 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2025-06-08 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1668,6 +973,7 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
+      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1686,6 +992,7 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
+      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1704,6 +1011,7 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
+      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1720,13 +1028,9 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2025-06-09 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1743,13 +1047,9 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2025-06-09 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1766,13 +1066,9 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2025-06-09 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1791,6 +1087,7 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
+      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1807,13 +1104,9 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2025-06-13 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1830,13 +1123,9 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2025-06-09 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1853,13 +1142,9 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2025-06-10 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1878,6 +1163,7 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
+      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1896,6 +1182,7 @@
       <c r="D37" t="n">
         <v>1</v>
       </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1914,6 +1201,7 @@
       <c r="D38" t="n">
         <v>1</v>
       </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1932,6 +1220,7 @@
       <c r="D39" t="n">
         <v>1</v>
       </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1948,13 +1237,9 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>2025-06-10 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1973,6 +1258,7 @@
       <c r="D41" t="n">
         <v>1</v>
       </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1989,13 +1275,9 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>2025-06-10 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2012,13 +1294,9 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2025-06-10 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2035,13 +1313,9 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2025-06-13 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2058,13 +1332,9 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2025-06-11 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2081,13 +1351,9 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2025-06-11 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2106,6 +1372,7 @@
       <c r="D47" t="n">
         <v>1</v>
       </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2124,6 +1391,7 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
+      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2140,13 +1408,9 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>2025-06-11 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2163,13 +1427,9 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2025-06-14 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2186,13 +1446,9 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2025-06-11 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2209,13 +1465,9 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2025-06-14 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2232,13 +1484,9 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2025-06-12 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2255,13 +1503,9 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2025-06-12 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2278,13 +1522,9 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2025-06-14 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2301,13 +1541,9 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2025-06-14 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2324,13 +1560,9 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2025-06-15 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2349,6 +1581,7 @@
       <c r="D58" t="n">
         <v>1</v>
       </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2365,13 +1598,9 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>2025-06-12 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2388,13 +1617,9 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2025-06-15 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2411,13 +1636,9 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2025-06-15 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2434,13 +1655,9 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2025-06-15 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2457,13 +1674,9 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2025-06-16 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2480,13 +1693,9 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2025-06-16 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2503,13 +1712,9 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2025-06-16 16:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2526,13 +1731,9 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2025-06-16 22:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2549,13 +1750,9 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2025-06-17 04:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2572,13 +1769,9 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2025-06-17 10:38:33</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2597,6 +1790,7 @@
       <c r="D69" t="n">
         <v>0</v>
       </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2615,6 +1809,7 @@
       <c r="D70" t="n">
         <v>0</v>
       </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2633,6 +1828,7 @@
       <c r="D71" t="n">
         <v>0</v>
       </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2651,6 +1847,7 @@
       <c r="D72" t="n">
         <v>0</v>
       </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2669,6 +1866,7 @@
       <c r="D73" t="n">
         <v>0</v>
       </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2687,6 +1885,7 @@
       <c r="D74" t="n">
         <v>0</v>
       </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2705,6 +1904,7 @@
       <c r="D75" t="n">
         <v>0</v>
       </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2723,6 +1923,7 @@
       <c r="D76" t="n">
         <v>0</v>
       </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2741,6 +1942,7 @@
       <c r="D77" t="n">
         <v>0</v>
       </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2759,6 +1961,7 @@
       <c r="D78" t="n">
         <v>0</v>
       </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2777,6 +1980,7 @@
       <c r="D79" t="n">
         <v>0</v>
       </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2795,6 +1999,7 @@
       <c r="D80" t="n">
         <v>0</v>
       </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2813,6 +2018,7 @@
       <c r="D81" t="n">
         <v>1</v>
       </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2831,6 +2037,7 @@
       <c r="D82" t="n">
         <v>0</v>
       </c>
+      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2849,6 +2056,7 @@
       <c r="D83" t="n">
         <v>0</v>
       </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2867,6 +2075,7 @@
       <c r="D84" t="n">
         <v>0</v>
       </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2885,6 +2094,7 @@
       <c r="D85" t="n">
         <v>1</v>
       </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2903,6 +2113,7 @@
       <c r="D86" t="n">
         <v>0</v>
       </c>
+      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2921,6 +2132,7 @@
       <c r="D87" t="n">
         <v>0</v>
       </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2939,6 +2151,7 @@
       <c r="D88" t="n">
         <v>0</v>
       </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2957,6 +2170,7 @@
       <c r="D89" t="n">
         <v>0</v>
       </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2975,6 +2189,7 @@
       <c r="D90" t="n">
         <v>0</v>
       </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2993,6 +2208,7 @@
       <c r="D91" t="n">
         <v>0</v>
       </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3011,6 +2227,7 @@
       <c r="D92" t="n">
         <v>1</v>
       </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3029,6 +2246,7 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
+      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3047,6 +2265,7 @@
       <c r="D94" t="n">
         <v>0</v>
       </c>
+      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3065,6 +2284,7 @@
       <c r="D95" t="n">
         <v>0</v>
       </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3083,6 +2303,7 @@
       <c r="D96" t="n">
         <v>0</v>
       </c>
+      <c r="E96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3101,6 +2322,7 @@
       <c r="D97" t="n">
         <v>0</v>
       </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3119,6 +2341,7 @@
       <c r="D98" t="n">
         <v>0</v>
       </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3137,6 +2360,7 @@
       <c r="D99" t="n">
         <v>0</v>
       </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3155,6 +2379,7 @@
       <c r="D100" t="n">
         <v>0</v>
       </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3173,6 +2398,7 @@
       <c r="D101" t="n">
         <v>0</v>
       </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3191,6 +2417,7 @@
       <c r="D102" t="n">
         <v>0</v>
       </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3209,6 +2436,7 @@
       <c r="D103" t="n">
         <v>0</v>
       </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3227,6 +2455,7 @@
       <c r="D104" t="n">
         <v>0</v>
       </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -3245,6 +2474,7 @@
       <c r="D105" t="n">
         <v>0</v>
       </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -3263,6 +2493,7 @@
       <c r="D106" t="n">
         <v>0</v>
       </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3281,6 +2512,7 @@
       <c r="D107" t="n">
         <v>0</v>
       </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -3299,6 +2531,7 @@
       <c r="D108" t="n">
         <v>0</v>
       </c>
+      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3317,6 +2550,7 @@
       <c r="D109" t="n">
         <v>0</v>
       </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3335,6 +2569,7 @@
       <c r="D110" t="n">
         <v>0</v>
       </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -3353,6 +2588,7 @@
       <c r="D111" t="n">
         <v>0</v>
       </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -3371,6 +2607,7 @@
       <c r="D112" t="n">
         <v>1</v>
       </c>
+      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -3389,6 +2626,7 @@
       <c r="D113" t="n">
         <v>0</v>
       </c>
+      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -3407,6 +2645,7 @@
       <c r="D114" t="n">
         <v>0</v>
       </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -3425,6 +2664,7 @@
       <c r="D115" t="n">
         <v>0</v>
       </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -3443,6 +2683,7 @@
       <c r="D116" t="n">
         <v>0</v>
       </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -3461,6 +2702,7 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
+      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -3479,6 +2721,7 @@
       <c r="D118" t="n">
         <v>0</v>
       </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -3497,6 +2740,7 @@
       <c r="D119" t="n">
         <v>0</v>
       </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -3515,6 +2759,7 @@
       <c r="D120" t="n">
         <v>0</v>
       </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -3533,6 +2778,7 @@
       <c r="D121" t="n">
         <v>0</v>
       </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -3551,6 +2797,7 @@
       <c r="D122" t="n">
         <v>0</v>
       </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -3569,6 +2816,7 @@
       <c r="D123" t="n">
         <v>0</v>
       </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -3587,6 +2835,7 @@
       <c r="D124" t="n">
         <v>0</v>
       </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -3605,6 +2854,7 @@
       <c r="D125" t="n">
         <v>0</v>
       </c>
+      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -3623,6 +2873,7 @@
       <c r="D126" t="n">
         <v>1</v>
       </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -3641,6 +2892,7 @@
       <c r="D127" t="n">
         <v>0</v>
       </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -3659,6 +2911,7 @@
       <c r="D128" t="n">
         <v>0</v>
       </c>
+      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -3677,6 +2930,7 @@
       <c r="D129" t="n">
         <v>0</v>
       </c>
+      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -3695,6 +2949,7 @@
       <c r="D130" t="n">
         <v>0</v>
       </c>
+      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3713,6 +2968,7 @@
       <c r="D131" t="n">
         <v>0</v>
       </c>
+      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3731,6 +2987,7 @@
       <c r="D132" t="n">
         <v>1</v>
       </c>
+      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -3749,6 +3006,7 @@
       <c r="D133" t="n">
         <v>0</v>
       </c>
+      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3767,6 +3025,7 @@
       <c r="D134" t="n">
         <v>0</v>
       </c>
+      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3785,6 +3044,7 @@
       <c r="D135" t="n">
         <v>1</v>
       </c>
+      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -3803,6 +3063,7 @@
       <c r="D136" t="n">
         <v>1</v>
       </c>
+      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -3821,6 +3082,7 @@
       <c r="D137" t="n">
         <v>0</v>
       </c>
+      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3839,6 +3101,7 @@
       <c r="D138" t="n">
         <v>0</v>
       </c>
+      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3857,6 +3120,7 @@
       <c r="D139" t="n">
         <v>0</v>
       </c>
+      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3875,6 +3139,7 @@
       <c r="D140" t="n">
         <v>0</v>
       </c>
+      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3893,6 +3158,7 @@
       <c r="D141" t="n">
         <v>0</v>
       </c>
+      <c r="E141" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3909,27 +3175,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>频道名称</t>
         </is>
       </c>
-      <c r="B1" s="2" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>MP4名称</t>
         </is>
       </c>
-      <c r="C1" s="2" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>是否发布</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>是否已经发布</t>
         </is>
       </c>
-      <c r="E1" s="2" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>发布时间</t>
         </is>
@@ -4180,13 +3446,9 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>2025-06-06 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -4203,13 +3465,9 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>2025-06-06 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -4226,13 +3484,9 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>2025-06-06 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -4249,13 +3503,9 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>2025-06-07 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -4272,13 +3522,9 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>2025-06-07 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -4295,13 +3541,9 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>2025-06-07 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -4318,13 +3560,9 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>2025-06-07 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -4341,13 +3579,9 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>2025-06-08 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -4364,13 +3598,9 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>2025-06-08 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -4387,13 +3617,9 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>2025-06-08 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4410,13 +3636,9 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>2025-06-08 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -4433,13 +3655,9 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>2025-06-09 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -4456,13 +3674,9 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>2025-06-09 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -4479,13 +3693,9 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>2025-06-09 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -4559,13 +3769,9 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>2025-06-09 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -4582,13 +3788,9 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>2025-06-10 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -4605,13 +3807,9 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>2025-06-10 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4647,13 +3845,9 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>2025-06-10 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -4670,13 +3864,9 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>2025-06-10 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4693,13 +3883,9 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>2025-06-11 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -4735,13 +3921,9 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>2025-06-11 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -4758,13 +3940,9 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>2025-06-11 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -4781,13 +3959,9 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>2025-06-11 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -4823,13 +3997,9 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>2025-06-12 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4865,13 +4035,9 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>2025-06-12 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4888,13 +4054,9 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>2025-06-12 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4911,13 +4073,9 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>2025-06-12 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4934,13 +4092,9 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>2025-06-13 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4957,13 +4111,9 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>2025-06-13 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -5018,13 +4168,9 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>2025-06-13 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -5041,13 +4187,9 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2025-06-13 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -5064,13 +4206,9 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>2025-06-14 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -5087,13 +4225,9 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>2025-06-14 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -5110,13 +4244,9 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>2025-06-14 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -5133,13 +4263,9 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>2025-06-14 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -5156,13 +4282,9 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>2025-06-15 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -5179,13 +4301,9 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>2025-06-15 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -5202,13 +4320,9 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>2025-06-15 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -5244,13 +4358,9 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>2025-06-15 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -5267,13 +4377,9 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>2025-06-16 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -5290,13 +4396,9 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>2025-06-16 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -5313,13 +4415,9 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>2025-06-16 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -5336,13 +4434,9 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>2025-06-16 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -5359,13 +4453,9 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>2025-06-17 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -5382,13 +4472,9 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>2025-06-17 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -5405,13 +4491,9 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>2025-06-17 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -5428,13 +4510,9 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>2025-06-17 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -5451,13 +4529,9 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>2025-06-18 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -5474,13 +4548,9 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>2025-06-18 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -5497,13 +4567,9 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>2025-06-18 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -5520,13 +4586,9 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>2025-06-18 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -5543,13 +4605,9 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>2025-06-19 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -5566,13 +4624,9 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>2025-06-19 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -5589,13 +4643,9 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>2025-06-19 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -5612,13 +4662,9 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>2025-06-19 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5635,13 +4681,9 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>2025-06-20 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5658,13 +4700,9 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>2025-06-20 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5681,13 +4719,9 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>2025-06-20 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5704,13 +4738,9 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>2025-06-20 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5727,13 +4757,9 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>2025-06-21 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5769,13 +4795,9 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>2025-06-21 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5792,13 +4814,9 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>2025-06-21 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5815,13 +4833,9 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>2025-06-21 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5857,13 +4871,9 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>2025-06-22 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5880,13 +4890,9 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>2025-06-22 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5903,13 +4909,9 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>2025-06-22 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5926,13 +4928,9 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>2025-06-22 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5949,13 +4947,9 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>2025-06-23 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5972,13 +4966,9 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>2025-06-23 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6033,13 +5023,9 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>2025-06-23 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6075,13 +5061,9 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>2025-06-23 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6098,13 +5080,9 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>2025-06-24 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6121,13 +5099,9 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>2025-06-24 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6144,13 +5118,9 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>2025-06-24 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6167,13 +5137,9 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>2025-06-24 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6190,13 +5156,9 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>2025-06-25 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6213,13 +5175,9 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>2025-06-25 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6236,13 +5194,9 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>2025-06-25 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6259,13 +5213,9 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>2025-06-25 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6282,13 +5232,9 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>2025-06-26 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6305,13 +5251,9 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>2025-06-26 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6328,13 +5270,9 @@
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>2025-06-26 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6351,13 +5289,9 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>2025-06-26 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6374,13 +5308,9 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>2025-06-27 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6397,13 +5327,9 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>2025-06-27 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6458,13 +5384,9 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>2025-06-27 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -6481,13 +5403,9 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>2025-06-27 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -6504,13 +5422,9 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>2025-06-28 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -6546,13 +5460,9 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>2025-06-28 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -6569,13 +5479,9 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>2025-06-28 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -6592,13 +5498,9 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>2025-06-28 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -6615,13 +5517,9 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>2025-06-29 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -6638,13 +5536,9 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>2025-06-29 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -6661,13 +5555,9 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>2025-06-29 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -6684,13 +5574,9 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>2025-06-29 22:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -6707,13 +5593,9 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>2025-06-30 04:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -6730,13 +5612,9 @@
         <v>1</v>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>2025-06-30 10:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -6753,13 +5631,9 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>2025-06-30 16:55:22</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -498,7 +498,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2025-06-12 22:38:33</t>
+          <t>2025-06-09 04:49:43</t>
         </is>
       </c>
     </row>
@@ -521,7 +521,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2025-06-13 04:38:33</t>
+          <t>2025-06-09 10:49:43</t>
         </is>
       </c>
     </row>
@@ -544,7 +544,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2025-06-13 10:38:33</t>
+          <t>2025-06-09 16:49:43</t>
         </is>
       </c>
     </row>
@@ -724,9 +724,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-06-10 04:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -743,9 +747,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-06-09 22:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -762,9 +770,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-06-10 10:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -781,9 +793,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-06-10 16:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -800,9 +816,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -819,9 +839,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-06-11 04:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3448,7 +3472,6 @@
       <c r="D12" t="n">
         <v>0</v>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -3465,9 +3488,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>2025-06-09 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3484,9 +3511,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2025-06-09 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3503,9 +3534,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
-      </c>
-      <c r="E15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>2025-06-09 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -3522,9 +3557,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>2025-06-09 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -3541,9 +3580,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>2025-06-10 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -3560,9 +3603,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>2025-06-10 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -3579,9 +3626,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-06-10 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -3598,9 +3649,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-06-10 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -3617,9 +3672,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-06-11 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -3636,9 +3695,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -3655,9 +3718,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-06-11 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -3674,9 +3741,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3693,9 +3764,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-06-12 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3714,7 +3789,6 @@
       <c r="D26" t="n">
         <v>1</v>
       </c>
-      <c r="E26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3733,7 +3807,6 @@
       <c r="D27" t="n">
         <v>1</v>
       </c>
-      <c r="E27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -3752,7 +3825,6 @@
       <c r="D28" t="n">
         <v>1</v>
       </c>
-      <c r="E28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -3769,9 +3841,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-06-12 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -3788,9 +3864,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-06-12 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -3807,9 +3887,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-06-12 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -3828,7 +3912,6 @@
       <c r="D32" t="n">
         <v>1</v>
       </c>
-      <c r="E32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -3845,9 +3928,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-06-13 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -3864,9 +3951,13 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-06-13 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -3883,9 +3974,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-06-13 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -3904,7 +3999,6 @@
       <c r="D36" t="n">
         <v>1</v>
       </c>
-      <c r="E36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -3921,9 +4015,13 @@
         <v>1</v>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>2025-06-13 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -3940,9 +4038,13 @@
         <v>1</v>
       </c>
       <c r="D38" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>2025-06-14 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3959,9 +4061,13 @@
         <v>1</v>
       </c>
       <c r="D39" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>2025-06-14 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3980,7 +4086,6 @@
       <c r="D40" t="n">
         <v>1</v>
       </c>
-      <c r="E40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3997,9 +4102,13 @@
         <v>1</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>2025-06-14 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -4018,7 +4127,6 @@
       <c r="D42" t="n">
         <v>1</v>
       </c>
-      <c r="E42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -4035,9 +4143,13 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-06-14 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4054,9 +4166,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-06-15 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4073,9 +4189,13 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-06-15 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4092,9 +4212,13 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-06-15 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4111,9 +4235,13 @@
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>2025-06-15 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4132,7 +4260,6 @@
       <c r="D48" t="n">
         <v>1</v>
       </c>
-      <c r="E48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4151,7 +4278,6 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -4168,9 +4294,13 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-06-16 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4187,9 +4317,13 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-06-16 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -4206,9 +4340,13 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-06-16 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4225,9 +4363,13 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-06-16 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -4244,9 +4386,13 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-06-17 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -4263,9 +4409,13 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-06-17 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -4282,9 +4432,13 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-06-17 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -4301,9 +4455,13 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-06-17 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -4320,9 +4478,13 @@
         <v>1</v>
       </c>
       <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>2025-06-18 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -4341,7 +4503,6 @@
       <c r="D59" t="n">
         <v>1</v>
       </c>
-      <c r="E59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4358,9 +4519,13 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-06-18 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4377,9 +4542,13 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-06-18 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4396,9 +4565,13 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-06-18 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4415,9 +4588,13 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-06-19 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4434,9 +4611,13 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-06-19 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4453,9 +4634,13 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-06-19 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4472,9 +4657,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-06-19 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4491,9 +4680,13 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-06-20 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4510,9 +4703,13 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-06-20 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4529,9 +4726,13 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2025-06-20 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4548,9 +4749,13 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025-06-20 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4567,9 +4772,13 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2025-06-21 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4586,9 +4795,13 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025-06-21 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4605,9 +4818,13 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2025-06-21 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4624,9 +4841,13 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2025-06-21 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4643,9 +4864,13 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-06-22 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4662,9 +4887,13 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2025-06-22 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4681,9 +4910,13 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2025-06-22 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4700,9 +4933,13 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2025-06-22 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -4719,9 +4956,13 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2025-06-23 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -4738,9 +4979,13 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2025-06-23 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -4757,9 +5002,13 @@
         <v>1</v>
       </c>
       <c r="D81" t="n">
-        <v>0</v>
-      </c>
-      <c r="E81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>2025-06-23 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -4778,7 +5027,6 @@
       <c r="D82" t="n">
         <v>1</v>
       </c>
-      <c r="E82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -4795,9 +5043,13 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2025-06-23 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -4814,9 +5066,13 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2025-06-24 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -4833,9 +5089,13 @@
         <v>1</v>
       </c>
       <c r="D85" t="n">
-        <v>0</v>
-      </c>
-      <c r="E85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>2025-06-24 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -4854,7 +5114,6 @@
       <c r="D86" t="n">
         <v>1</v>
       </c>
-      <c r="E86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -4871,9 +5130,13 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2025-06-24 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -4890,9 +5153,13 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2025-06-24 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -4909,9 +5176,13 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2025-06-25 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -4928,9 +5199,13 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2025-06-25 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -4947,9 +5222,13 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2025-06-25 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -4966,9 +5245,13 @@
         <v>1</v>
       </c>
       <c r="D92" t="n">
-        <v>0</v>
-      </c>
-      <c r="E92" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>2025-06-25 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -4987,7 +5270,6 @@
       <c r="D93" t="n">
         <v>1</v>
       </c>
-      <c r="E93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5006,7 +5288,6 @@
       <c r="D94" t="n">
         <v>1</v>
       </c>
-      <c r="E94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5023,9 +5304,13 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2025-06-26 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5042,9 +5327,13 @@
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2025-06-26 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -5061,9 +5350,13 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2025-06-26 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -5080,9 +5373,13 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2025-06-26 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -5099,9 +5396,13 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2025-06-27 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -5118,9 +5419,13 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2025-06-27 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -5139,7 +5444,6 @@
       <c r="D101" t="n">
         <v>0</v>
       </c>
-      <c r="E101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -5156,9 +5460,13 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2025-06-27 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -5175,9 +5483,13 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2025-06-27 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -5194,9 +5506,13 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2025-06-28 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -5213,9 +5529,13 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2025-06-28 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -5232,9 +5552,13 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2025-06-28 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -5251,9 +5575,13 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2025-06-28 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -5270,9 +5598,13 @@
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2025-06-29 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -5289,9 +5621,13 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2025-06-29 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -5308,9 +5644,13 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2025-06-29 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -5327,9 +5667,13 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2025-06-29 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -5348,7 +5692,6 @@
       <c r="D112" t="n">
         <v>0</v>
       </c>
-      <c r="E112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -5367,7 +5710,6 @@
       <c r="D113" t="n">
         <v>1</v>
       </c>
-      <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -5384,9 +5726,13 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2025-06-30 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -5403,9 +5749,13 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2025-06-30 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -5422,9 +5772,13 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2025-06-30 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -5443,7 +5797,6 @@
       <c r="D117" t="n">
         <v>1</v>
       </c>
-      <c r="E117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -5460,9 +5813,13 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2025-06-30 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -5479,9 +5836,13 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2025-07-01 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -5498,9 +5859,13 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2025-07-01 10:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -5517,9 +5882,13 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2025-07-01 16:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -5536,9 +5905,13 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2025-07-01 22:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -5555,9 +5928,13 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2025-07-02 04:59:14</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -5576,7 +5953,6 @@
       <c r="D124" t="n">
         <v>0</v>
       </c>
-      <c r="E124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -5595,7 +5971,6 @@
       <c r="D125" t="n">
         <v>0</v>
       </c>
-      <c r="E125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -5614,7 +5989,6 @@
       <c r="D126" t="n">
         <v>0</v>
       </c>
-      <c r="E126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -5633,7 +6007,6 @@
       <c r="D127" t="n">
         <v>0</v>
       </c>
-      <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5652,7 +6025,6 @@
       <c r="D128" t="n">
         <v>1</v>
       </c>
-      <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5671,7 +6043,6 @@
       <c r="D129" t="n">
         <v>0</v>
       </c>
-      <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5690,7 +6061,6 @@
       <c r="D130" t="n">
         <v>0</v>
       </c>
-      <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5709,7 +6079,6 @@
       <c r="D131" t="n">
         <v>0</v>
       </c>
-      <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5728,7 +6097,6 @@
       <c r="D132" t="n">
         <v>0</v>
       </c>
-      <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5747,7 +6115,6 @@
       <c r="D133" t="n">
         <v>0</v>
       </c>
-      <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5766,7 +6133,6 @@
       <c r="D134" t="n">
         <v>1</v>
       </c>
-      <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5785,7 +6151,6 @@
       <c r="D135" t="n">
         <v>0</v>
       </c>
-      <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5804,7 +6169,6 @@
       <c r="D136" t="n">
         <v>0</v>
       </c>
-      <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5823,7 +6187,6 @@
       <c r="D137" t="n">
         <v>1</v>
       </c>
-      <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5842,7 +6205,6 @@
       <c r="D138" t="n">
         <v>1</v>
       </c>
-      <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5861,7 +6223,6 @@
       <c r="D139" t="n">
         <v>0</v>
       </c>
-      <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5880,7 +6241,6 @@
       <c r="D140" t="n">
         <v>0</v>
       </c>
-      <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5899,7 +6259,6 @@
       <c r="D141" t="n">
         <v>0</v>
       </c>
-      <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5918,7 +6277,6 @@
       <c r="D142" t="n">
         <v>0</v>
       </c>
-      <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5937,7 +6295,6 @@
       <c r="D143" t="n">
         <v>0</v>
       </c>
-      <c r="E143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -862,9 +862,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>2025-06-11 10:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -900,9 +904,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>2025-06-11 16:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -919,9 +927,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>2025-06-11 22:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -938,9 +950,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
-      </c>
-      <c r="E23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>2025-06-12 04:49:43</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">

--- a/buda/mp4_publish_tracker.xlsx
+++ b/buda/mp4_publish_tracker.xlsx
@@ -885,9 +885,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>2025-06-14 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -973,9 +977,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>2025-06-14 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -992,9 +1000,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>2025-06-15 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1068,9 +1080,13 @@
         <v>1</v>
       </c>
       <c r="D29" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>2025-06-15 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1087,9 +1103,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
-      </c>
-      <c r="E30" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>2025-06-15 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1106,9 +1126,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>2025-06-15 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1144,9 +1168,13 @@
         <v>1</v>
       </c>
       <c r="D33" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>2025-06-16 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1163,9 +1191,13 @@
         <v>1</v>
       </c>
       <c r="D34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>2025-06-16 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1182,9 +1214,13 @@
         <v>1</v>
       </c>
       <c r="D35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>2025-06-16 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1277,9 +1313,13 @@
         <v>1</v>
       </c>
       <c r="D40" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>2025-06-16 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1315,9 +1355,13 @@
         <v>1</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>2025-06-17 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1334,9 +1378,13 @@
         <v>1</v>
       </c>
       <c r="D43" t="n">
-        <v>0</v>
-      </c>
-      <c r="E43" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>2025-06-17 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1353,9 +1401,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>2025-06-17 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1372,9 +1424,13 @@
         <v>1</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>2025-06-17 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1391,9 +1447,13 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>2025-06-18 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1448,9 +1508,13 @@
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>2025-06-18 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1467,9 +1531,13 @@
         <v>1</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>2025-06-18 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1486,9 +1554,13 @@
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>2025-06-18 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1505,9 +1577,13 @@
         <v>1</v>
       </c>
       <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>2025-06-19 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1524,9 +1600,13 @@
         <v>1</v>
       </c>
       <c r="D53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>2025-06-19 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1543,9 +1623,13 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>2025-06-19 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1562,9 +1646,13 @@
         <v>1</v>
       </c>
       <c r="D55" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2025-06-19 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1581,9 +1669,13 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>2025-06-20 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1600,9 +1692,13 @@
         <v>1</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>2025-06-20 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1638,9 +1734,13 @@
         <v>1</v>
       </c>
       <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>2025-06-20 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1657,9 +1757,13 @@
         <v>1</v>
       </c>
       <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>2025-06-20 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1676,9 +1780,13 @@
         <v>1</v>
       </c>
       <c r="D61" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>2025-06-21 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1695,9 +1803,13 @@
         <v>1</v>
       </c>
       <c r="D62" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>2025-06-21 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1714,9 +1826,13 @@
         <v>1</v>
       </c>
       <c r="D63" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>2025-06-21 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1733,9 +1849,13 @@
         <v>1</v>
       </c>
       <c r="D64" t="n">
-        <v>0</v>
-      </c>
-      <c r="E64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>2025-06-21 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1752,9 +1872,13 @@
         <v>1</v>
       </c>
       <c r="D65" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>2025-06-22 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1771,9 +1895,13 @@
         <v>1</v>
       </c>
       <c r="D66" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>2025-06-22 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1790,9 +1918,13 @@
         <v>1</v>
       </c>
       <c r="D67" t="n">
-        <v>0</v>
-      </c>
-      <c r="E67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>2025-06-22 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1809,9 +1941,13 @@
         <v>1</v>
       </c>
       <c r="D68" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>2025-06-22 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1828,9 +1964,13 @@
         <v>1</v>
       </c>
       <c r="D69" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>2025-06-23 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1847,9 +1987,13 @@
         <v>1</v>
       </c>
       <c r="D70" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>2025-06-23 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1866,9 +2010,13 @@
         <v>1</v>
       </c>
       <c r="D71" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>2025-06-23 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1885,9 +2033,13 @@
         <v>1</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>2025-06-23 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1904,9 +2056,13 @@
         <v>1</v>
       </c>
       <c r="D73" t="n">
-        <v>0</v>
-      </c>
-      <c r="E73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>2025-06-24 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1923,9 +2079,13 @@
         <v>1</v>
       </c>
       <c r="D74" t="n">
-        <v>0</v>
-      </c>
-      <c r="E74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>2025-06-24 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1942,9 +2102,13 @@
         <v>1</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
-      </c>
-      <c r="E75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>2025-06-24 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1961,9 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0</v>
-      </c>
-      <c r="E76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>2025-06-24 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1980,9 +2148,13 @@
         <v>1</v>
       </c>
       <c r="D77" t="n">
-        <v>0</v>
-      </c>
-      <c r="E77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>2025-06-25 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1999,9 +2171,13 @@
         <v>1</v>
       </c>
       <c r="D78" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>2025-06-25 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2018,9 +2194,13 @@
         <v>1</v>
       </c>
       <c r="D79" t="n">
-        <v>0</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>2025-06-25 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2037,9 +2217,13 @@
         <v>1</v>
       </c>
       <c r="D80" t="n">
-        <v>0</v>
-      </c>
-      <c r="E80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>2025-06-25 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2075,9 +2259,13 @@
         <v>1</v>
       </c>
       <c r="D82" t="n">
-        <v>0</v>
-      </c>
-      <c r="E82" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>2025-06-26 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2094,9 +2282,13 @@
         <v>1</v>
       </c>
       <c r="D83" t="n">
-        <v>0</v>
-      </c>
-      <c r="E83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>2025-06-26 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2113,9 +2305,13 @@
         <v>1</v>
       </c>
       <c r="D84" t="n">
-        <v>0</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>2025-06-26 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2151,9 +2347,13 @@
         <v>1</v>
       </c>
       <c r="D86" t="n">
-        <v>0</v>
-      </c>
-      <c r="E86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>2025-06-26 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2170,9 +2370,13 @@
         <v>1</v>
       </c>
       <c r="D87" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>2025-06-27 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2189,9 +2393,13 @@
         <v>1</v>
       </c>
       <c r="D88" t="n">
-        <v>0</v>
-      </c>
-      <c r="E88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>2025-06-27 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2208,9 +2416,13 @@
         <v>1</v>
       </c>
       <c r="D89" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>2025-06-27 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2227,9 +2439,13 @@
         <v>1</v>
       </c>
       <c r="D90" t="n">
-        <v>0</v>
-      </c>
-      <c r="E90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>2025-06-27 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2246,9 +2462,13 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>2025-06-28 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2303,9 +2523,13 @@
         <v>1</v>
       </c>
       <c r="D94" t="n">
-        <v>0</v>
-      </c>
-      <c r="E94" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>2025-06-28 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2322,9 +2546,13 @@
         <v>1</v>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
-      </c>
-      <c r="E95" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>2025-06-28 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2341,9 +2569,13 @@
         <v>1</v>
       </c>
       <c r="D96" t="n">
-        <v>0</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>2025-06-28 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2360,9 +2592,13 @@
         <v>1</v>
       </c>
       <c r="D97" t="n">
-        <v>0</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>2025-06-29 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2379,9 +2615,13 @@
         <v>1</v>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
-      </c>
-      <c r="E98" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>2025-06-29 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2398,9 +2638,13 @@
         <v>1</v>
       </c>
       <c r="D99" t="n">
-        <v>0</v>
-      </c>
-      <c r="E99" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>2025-06-29 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2417,9 +2661,13 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>0</v>
-      </c>
-      <c r="E100" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>2025-06-29 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2436,9 +2684,13 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0</v>
-      </c>
-      <c r="E101" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>2025-06-30 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2455,9 +2707,13 @@
         <v>1</v>
       </c>
       <c r="D102" t="n">
-        <v>0</v>
-      </c>
-      <c r="E102" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>2025-06-30 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2474,9 +2730,13 @@
         <v>1</v>
       </c>
       <c r="D103" t="n">
-        <v>0</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>2025-06-30 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2493,9 +2753,13 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>0</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>2025-06-30 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2512,9 +2776,13 @@
         <v>1</v>
       </c>
       <c r="D105" t="n">
-        <v>0</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>2025-07-01 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2531,9 +2799,13 @@
         <v>1</v>
       </c>
       <c r="D106" t="n">
-        <v>0</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>2025-07-01 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2550,9 +2822,13 @@
         <v>1</v>
       </c>
       <c r="D107" t="n">
-        <v>0</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>2025-07-01 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2569,9 +2845,13 @@
         <v>1</v>
       </c>
       <c r="D108" t="n">
-        <v>0</v>
-      </c>
-      <c r="E108" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>2025-07-01 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2588,9 +2868,13 @@
         <v>1</v>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
-      </c>
-      <c r="E109" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>2025-07-02 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2607,9 +2891,13 @@
         <v>1</v>
       </c>
       <c r="D110" t="n">
-        <v>0</v>
-      </c>
-      <c r="E110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>2025-07-02 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2626,9 +2914,13 @@
         <v>1</v>
       </c>
       <c r="D111" t="n">
-        <v>0</v>
-      </c>
-      <c r="E111" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>2025-07-02 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2664,9 +2956,13 @@
         <v>1</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
-      </c>
-      <c r="E113" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>2025-07-02 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2683,9 +2979,13 @@
         <v>1</v>
       </c>
       <c r="D114" t="n">
-        <v>0</v>
-      </c>
-      <c r="E114" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>2025-07-03 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2702,9 +3002,13 @@
         <v>1</v>
       </c>
       <c r="D115" t="n">
-        <v>0</v>
-      </c>
-      <c r="E115" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>2025-07-03 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2721,9 +3025,13 @@
         <v>1</v>
       </c>
       <c r="D116" t="n">
-        <v>0</v>
-      </c>
-      <c r="E116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>2025-07-03 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2759,9 +3067,13 @@
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0</v>
-      </c>
-      <c r="E118" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>2025-07-03 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -2778,9 +3090,13 @@
         <v>1</v>
       </c>
       <c r="D119" t="n">
-        <v>0</v>
-      </c>
-      <c r="E119" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>2025-07-04 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2797,9 +3113,13 @@
         <v>1</v>
       </c>
       <c r="D120" t="n">
-        <v>0</v>
-      </c>
-      <c r="E120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>2025-07-04 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2816,9 +3136,13 @@
         <v>1</v>
       </c>
       <c r="D121" t="n">
-        <v>0</v>
-      </c>
-      <c r="E121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>2025-07-04 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2835,9 +3159,13 @@
         <v>1</v>
       </c>
       <c r="D122" t="n">
-        <v>0</v>
-      </c>
-      <c r="E122" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>2025-07-04 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2854,9 +3182,13 @@
         <v>1</v>
       </c>
       <c r="D123" t="n">
-        <v>0</v>
-      </c>
-      <c r="E123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>2025-07-05 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2873,9 +3205,13 @@
         <v>1</v>
       </c>
       <c r="D124" t="n">
-        <v>0</v>
-      </c>
-      <c r="E124" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>2025-07-05 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2892,9 +3228,13 @@
         <v>1</v>
       </c>
       <c r="D125" t="n">
-        <v>0</v>
-      </c>
-      <c r="E125" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>2025-07-05 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2930,9 +3270,13 @@
         <v>1</v>
       </c>
       <c r="D127" t="n">
-        <v>0</v>
-      </c>
-      <c r="E127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>2025-07-05 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2949,9 +3293,13 @@
         <v>1</v>
       </c>
       <c r="D128" t="n">
-        <v>0</v>
-      </c>
-      <c r="E128" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>2025-07-06 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2968,9 +3316,13 @@
         <v>1</v>
       </c>
       <c r="D129" t="n">
-        <v>0</v>
-      </c>
-      <c r="E129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>2025-07-06 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2987,9 +3339,13 @@
         <v>1</v>
       </c>
       <c r="D130" t="n">
-        <v>0</v>
-      </c>
-      <c r="E130" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>2025-07-06 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -3006,9 +3362,13 @@
         <v>1</v>
       </c>
       <c r="D131" t="n">
-        <v>0</v>
-      </c>
-      <c r="E131" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>2025-07-06 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -3044,9 +3404,13 @@
         <v>1</v>
       </c>
       <c r="D133" t="n">
-        <v>0</v>
-      </c>
-      <c r="E133" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>2025-07-07 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -3063,9 +3427,13 @@
         <v>1</v>
       </c>
       <c r="D134" t="n">
-        <v>0</v>
-      </c>
-      <c r="E134" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>2025-07-07 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -3120,9 +3488,13 @@
         <v>1</v>
       </c>
       <c r="D137" t="n">
-        <v>0</v>
-      </c>
-      <c r="E137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>2025-07-07 15:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -3139,9 +3511,13 @@
         <v>1</v>
       </c>
       <c r="D138" t="n">
-        <v>0</v>
-      </c>
-      <c r="E138" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>2025-07-07 21:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -3158,9 +3534,13 @@
         <v>1</v>
       </c>
       <c r="D139" t="n">
-        <v>0</v>
-      </c>
-      <c r="E139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>2025-07-08 03:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -3177,9 +3557,13 @@
         <v>1</v>
       </c>
       <c r="D140" t="n">
-        <v>0</v>
-      </c>
-      <c r="E140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>2025-07-08 09:45:14</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -3196,9 +3580,13 @@
         <v>1</v>
       </c>
       <c r="D141" t="n">
-        <v>0</v>
-      </c>
-      <c r="E141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>2025-07-08 15:45:14</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
